--- a/скрипт КабС, ДОКИ, Смартвей.xlsx
+++ b/скрипт КабС, ДОКИ, Смартвей.xlsx
@@ -613,7 +613,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Компактный сценарий на 4 ЛПР · тон: спокойный, партнёрский, без давления</t>
+          <t>Короткий сценарий на 4 ЛПР · читать можно почти дословно · тон спокойный и уважительный</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -667,29 +667,29 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Добрый день, [ИО]! Компания «[название]», верно? Меня зовут [имя], я из «Форуса» — мы ваш партнёр по 1С. Звоню по нескольким сервисам, которые помогают убирать бумажную рутину. У вас есть пара минут?</t>
+          <t>Добрый день, [ИО]! Компания «[название]», верно? Меня зовут [имя], я из «Форуса» — мы ваш партнёр по 1С. Звоню по поводу нескольких сервисов, которые помогают убрать бумажную рутину. Подскажите, у вас есть пара минут?</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Добрый день, [ИО]! Компания «[название]», верно? Меня зовут [имя], я из «Форуса» — мы ваш партнёр по 1С. Звоню по нескольким сервисам, которые помогают убирать бумажную рутину. У вас есть пара минут?</t>
+          <t>Добрый день, [ИО]! Компания «[название]», верно? Меня зовут [имя], я из «Форуса» — мы ваш партнёр по 1С. Звоню по поводу нескольких сервисов, которые помогают убрать бумажную рутину. Подскажите, у вас есть пара минут?</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Добрый день, [ИО]! Компания «[название]», верно? Меня зовут [имя], я из «Форуса» — мы ваш партнёр по 1С. Звоню по нескольким сервисам, которые помогают убирать бумажную рутину. У вас есть пара минут?</t>
+          <t>Добрый день, [ИО]! Компания «[название]», верно? Меня зовут [имя], я из «Форуса» — мы ваш партнёр по 1С. Звоню по поводу нескольких сервисов, которые помогают убрать бумажную рутину. Подскажите, у вас есть пара минут?</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Добрый день, [ИО]! Компания «[название]», верно? Меня зовут [имя], я из «Форуса» — мы ваш партнёр по 1С. Звоню по нескольким сервисам, которые помогают убирать бумажную рутину. У вас есть пара минут?</t>
+          <t>Добрый день, [ИО]! Компания «[название]», верно? Меня зовут [имя], я из «Форуса» — мы ваш партнёр по 1С. Звоню по поводу нескольких сервисов, которые помогают убрать бумажную рутину. Подскажите, у вас есть пара минут?</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2. ДОКИ (сначала) — заход через ИТС ПРОФ</t>
+          <t>2. ДОКИ — заход через ИТС ПРОФ</t>
         </is>
       </c>
       <c r="B6" s="4" t="n"/>
@@ -705,26 +705,26 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>[ИО], смотрю, у вас подключен ИТС ПРОФ — он скоро заканчивается. В него входит бесплатное подключение сервиса «1С:ДОКИ» на 3 месяца с безлимитным обменом документов. Давайте за пару минут посмотрим, полезно ли это вам?</t>
+          <t>[ИО], смотрю, у вас подключён ИТС ПРОФ — он скоро заканчивается. В него входит бесплатное подключение сервиса «ДОКИ» на три месяца с безлимитным обменом документов. Можно буквально за пару минут посмотреть, будет ли вам это удобно?</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>[ИО], смотрю, у вас подключен ИТС ПРОФ — он скоро заканчивается. В него входит бесплатное подключение сервиса «1С:ДОКИ» на 3 месяца с безлимитным обменом документов. Давайте за пару минут посмотрим, полезно ли это вам?</t>
+          <t>[ИО], смотрю, у вас подключён ИТС ПРОФ — он скоро заканчивается. В него входит бесплатное подключение сервиса «ДОКИ» на три месяца с безлимитным обменом документов. Можно буквально за пару минут посмотреть, будет ли вам это удобно?</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>[ИО], буквально минуту: по ИТС ПРОФ у вас доступно бесплатное подключение «ДОКИ» на 3 месяца. Это про обмен документами с контрагентами — для кадров обычно не основной инструмент, но спрошу пару вопросов и перейду к сервису, который как раз для вас.</t>
+          <t>[ИО], совсем коротко: по ИТС ПРОФ у вас есть бесплатное подключение «ДОКИ» на три месяца. Это больше про обмен документами с контрагентами. Если для вас это не актуально — сразу перейдём к сервису, который как раз для кадровой работы. Можно?</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>[ИО], смотрю, у вас подключен ИТС ПРОФ — он скоро заканчивается. В него входит бесплатное подключение сервиса «1С:ДОКИ» на 3 месяца с безлимитным обменом документов. Давайте за пару минут посмотрим, полезно ли это вам?</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="86" customHeight="1">
+          <t>[ИО], смотрю, у вас подключён ИТС ПРОФ — он скоро заканчивается. В него входит бесплатное подключение сервиса «ДОКИ» на три месяца с безлимитным обменом документов. Можно буквально за пару минут посмотреть, будет ли вам это удобно?</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Вопросы ДОКИ</t>
@@ -732,26 +732,26 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Как сейчас обмениваетесь документами с партнёрами — бумага или уже ЭДО (Диадок, СБИС, 1С-ЭДО)? Бывают ли задержки и потери?</t>
+          <t>Подскажите, пожалуйста: как вы сейчас обмениваетесь документами с партнёрами — на бумаге или уже через ЭДО, например Диадок, СБИС, 1С-ЭДО? Бывают ли задержки или потери?</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Работаете с ЭДО из 1С или через веб-кабинет? Часто ли контрагенты просят документы «на вчера»?</t>
+          <t>А вы работаете с ЭДО прямо из 1С или через отдельный веб-кабинет? Часто ли просят отправить документы срочно?</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>С кадровиком блок ДОКИ коротко: «Ок, тогда этот сервис больше для бухгалтерии/руководства — перейдём к Кабинету сотрудника».</t>
+          <t>Для кадровика: «Хорошо, тогда «ДОКИ» скорее для бухгалтерии. Давайте лучше про Кабинет сотрудника — он как раз про вашу работу».</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>Насколько удобно сейчас отправлять документы из вашей 1С? Есть ли отдельный веб-кабинет оператора, куда приходится заходить отдельно?</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="92" customHeight="1">
+          <t>Насколько сейчас удобно отправлять документы из вашей 1С? Не приходится ли отдельно заходить в кабинет оператора?</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="100" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Презентация ДОКИ</t>
@@ -759,29 +759,29 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>«1С:ДОКИ» — ЭДО от 1С и «Калуга Астрал». Сервис можно подвязать к вашей 1С (кнопка «Отправить» в документах) или пользоваться веб-версией без привязки к 1С. Попробуйте и сравните удобство: 3 месяца безлимита бесплатно. Если не понравится — можно не продлевать, ни к чему не обязывает. Настройку берём на себя.</t>
+          <t>Понял(а) вас. Есть сервис «1С:ДОКИ» — это электронный документооборот от 1С и «Калуга Астрал». Его можно подключить к вашей 1С — прямо в документах появится кнопка «Отправить». А можно пользоваться веб-версией, даже без привязки к 1С. Предлагаю просто попробовать и сравнить удобство: три месяца безлимита — бесплатно. Если не понравится — можно не продлевать, ни к чему не обязывает. Настройку мы берём на себя.</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>«1С:ДОКИ» — ЭДО от 1С и «Калуга Астрал». Сервис можно подвязать к вашей 1С (кнопка «Отправить» в документах) или пользоваться веб-версией без привязки к 1С. Попробуйте и сравните удобство: 3 месяца безлимита бесплатно. Если не понравится — можно не продлевать, ни к чему не обязывает. Настройку берём на себя.</t>
+          <t>Понял(а) вас. Есть сервис «1С:ДОКИ» — это электронный документооборот от 1С и «Калуга Астрал». Его можно подключить к вашей 1С — прямо в документах появится кнопка «Отправить». А можно пользоваться веб-версией, даже без привязки к 1С. Предлагаю просто попробовать и сравнить удобство: три месяца безлимита — бесплатно. Если не понравится — можно не продлевать, ни к чему не обязывает. Настройку мы берём на себя.</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Кратко: «Это для обмена с контрагентами. Если интересно бухгалтеру — подключим. Дальше — сервис именно для кадров».</t>
+          <t>Кратко: «Это для обмена с контрагентами. Если бухгалтеру будет интересно — подключим. А сейчас расскажу про сервис именно для кадров».</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>«1С:ДОКИ» — ЭДО от 1С и «Калуга Астрал». Сервис можно подвязать к вашей 1С (кнопка «Отправить» в документах) или пользоваться веб-версией без привязки к 1С. Попробуйте и сравните удобство: 3 месяца безлимита бесплатно. Если не понравится — можно не продлевать, ни к чему не обязывает. Настройку берём на себя.</t>
+          <t>Понял(а) вас. Есть сервис «1С:ДОКИ» — это электронный документооборот от 1С и «Калуга Астрал». Его можно подключить к вашей 1С — прямо в документах появится кнопка «Отправить». А можно пользоваться веб-версией, даже без привязки к 1С. Предлагаю просто попробовать и сравнить удобство: три месяца безлимита — бесплатно. Если не понравится — можно не продлевать, ни к чему не обязывает. Настройку мы берём на себя.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>3. 1С:КАБИНЕТ СОТРУДНИКА — сбор потребности → презентация → демо</t>
+          <t>3. 1С:КАБИНЕТ СОТРУДНИКА — вопросы → рассказ → демо</t>
         </is>
       </c>
       <c r="B10" s="4" t="n"/>
@@ -789,7 +789,7 @@
       <c r="D10" s="4" t="n"/>
       <c r="E10" s="4" t="n"/>
     </row>
-    <row r="11" ht="110" customHeight="1">
+    <row r="11" ht="115" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Вопросы КабС</t>
@@ -797,26 +797,26 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Как сейчас устроен документооборот с сотрудниками — заявления, приказы, согласования? Бумага или уже электронно? Сколько времени уходит на согласования?</t>
+          <t>[ИО], а как у вас сейчас устроен документооборот с сотрудниками — заявления, приказы, согласования? На бумаге или уже электронно? Сколько обычно уходит времени на согласование?</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>По ст. 136 ТК вы обязаны извещать сотрудников о зарплате. Как выдаёте расчётные листки и есть ли подтверждение ознакомления? Сможете за 10 минут найти, что Иванов подписал расчётку?</t>
+          <t>[ИО], по статье 136 Трудового кодекса нужно извещать сотрудников о зарплате. Как сейчас выдаёте расчётные листки? И есть ли подтверждение, что человек ознакомился? Сможете, например, за 10 минут найти, что Иванов подписал расчётку?</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Как сотрудники подают заявления на отпуск/справки? Сколько времени на приём и график отпусков? Как с удалёнщиками — приём, увольнение, подписание?</t>
+          <t>[ИО], расскажите, пожалуйста: как сотрудники подают заявления на отпуск или просят справки? Сколько времени уходит на приём и на график отпусков? А с удалёнными сотрудниками как работаете — приём, увольнение, подписание?</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>Где хранятся кадровые документы сейчас? Насколько критична безопасность персданных и связка с вашей 1С / ЗУП?</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="130" customHeight="1">
+          <t>[ИО], а где сейчас хранятся кадровые документы? Насколько для вас важны безопасность персональных данных и чтобы всё было связано с вашей 1С?</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="135" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Презентация КабС</t>
@@ -824,26 +824,26 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>«1С:Кабинет сотрудника» — как Госуслуги для ваших сотрудников: смотрят нужную информацию, сами подают заявления, подписывают документы. Легче в обучении и использовании. Учитывая цифровизацию в РФ (ЭДО, ЭПД) — КЭДО следующий шаг. Ст. 136, 173 ТК — будьте на шаг впереди без спешки. Стоимость — меньше 30 ₽/мес на сотрудника. Плюс меньше бумаги — экологический след компании тоже снижается.</t>
+          <t>Есть сервис «1С:Кабинет сотрудника». Это как Госуслуги для ваших сотрудников: можно смотреть нужную информацию, самим подавать заявления, подписывать документы. При этом учиться пользоваться проще, чем многими другими системами. Сейчас в стране активно идёт цифровизация — ЭДО, электронные перевозочные документы, и кадровый электронный документооборот — следующий шаг. Есть статьи 136 и 173 Трудового кодекса — лучше подготовиться спокойно, без спешки. Стоимость кабинета — меньше 30 рублей в месяц на сотрудника. И бумаги станет меньше — для экологии компании тоже плюс.</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>Расчётные листки уходят в личный кабинет с ознакомлением — требование закона выполняется без распечатки. Заявления и вычеты — из приложения. Данные сразу в 1С, меньше ошибок. Можно начать с одного отдела за низкую стоимость и потом перевести всю компанию.</t>
+          <t>Через сервис расчётные листки уходят сотруднику в личный кабинет, и видно, что он ознакомился. Требование закона выполняется без распечатки. Заявления и вычеты можно подать из приложения, данные сразу попадают в 1С — меньше ошибок. Можно начать с одного отдела, за небольшую стоимость, а потом перевести всю компанию.</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Сотрудники сами подают заявления и смотрят остатки отпусков — меньше отвлечений. Заявления приходят сразу в 1С и превращаются в приказы. Для мягкого старта советуем подключить один отдел / небольшое число сотрудников, попробовать, затем без проблем масштабировать. Меньше 30 ₽/мес на человека.</t>
+          <t>Сотрудники сами подают заявления и смотрят остатки отпуска — вас меньше отвлекают. Заявления приходят сразу в 1С и превращаются в приказы. Для спокойного перехода советуем подключить сначала один отдел или небольшое число сотрудников, посмотреть, как удобно, и потом перевести всю компанию. Стоимость — меньше 30 рублей в месяц на человека.</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>Сервис встроен в вашу 1С: документы хранятся в вашей базе, не в чужом облаке. Есть локальная версия, ЦОД 1С с аттестатами ФСТЭК. Настройку берём на себя — IT не перегружаем.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="86" customHeight="1">
+          <t>Сервис уже связан с вашей 1С. Документы хранятся в вашей базе, а не в чужом облаке. Есть и локальная версия, дата-центр 1С с аттестатами ФСТЭК. Настройку берём на себя — ваших специалистов сильно не загрузим.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="95" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Коммерческий заход</t>
@@ -851,26 +851,26 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Для лёгкого перехода на КЭДО рекомендуем начать с одного отдела — низкая стоимость, без стресса. Когда КЭДО станет обязательным (к этому всё идёт) — вы уже будете готовы.</t>
+          <t>Чтобы переход был лёгким и без напряжения, советуем начать с одного отдела — попробовать на небольшом числе сотрудников за небольшую стоимость, а потом без проблем перевести на КЭДО всю компанию. Когда это станет обязательным — а к этому всё идёт — вы уже будете готовы и сможете не думать об этом.</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Сколько сотрудников хотите подключить на старт? Ориентир — от 21–30 ₽/мес за сотрудника. Можем посчитать на ваш штат.</t>
+          <t>Подскажите, сколько сотрудников хотели бы подключить на старте? Ориентир — от 21 до 30 рублей в месяц за человека. Можем посчитать именно на ваш штат.</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Не нужно сразу всех: один отдел → проверили удобство → перевели компанию. Мы помогаем с шаблонами документов перехода на КЭДО.</t>
+          <t>Не обязательно сразу всех. Один отдел — посмотрели, удобно ли — и перевели компанию. Мы поможем и с документами для перехода: есть готовые шаблоны.</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Интеграция с 1С уже есть, внедрение типовое. На старте — пилот на небольшом контуре, без тяжёлого проекта.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="64" customHeight="1">
+          <t>С 1С всё уже стыкуется, проект не тяжёлый. На старте можно взять небольшой отдел и спокойно проверить.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="70" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Закрытие на демо</t>
@@ -878,22 +878,22 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Давайте покажу на 15-минутной демонстрации, как это выглядит в работе. Когда удобно посмотреть?</t>
+          <t>Давайте покажу на 15-минутной демонстрации, как это выглядит в работе. Когда вам удобно будет посмотреть?</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Давайте на 15 минут покажу, как закрывается ст. 136 и как листки уходят в кабинет. Когда удобно?</t>
+          <t>Давайте покажу, как это работает, на 15-минутной демонстрации. Оцените, насколько это упрощает выполнение требований закона. Когда вам удобно?</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Давайте покажу, как заявления сами попадают в 1С. 15 минут — когда удобно?</t>
+          <t>Давайте покажу на 15-минутной демонстрации, как заявления сотрудников автоматически попадают в 1С. Когда вам удобно будет посмотреть?</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Покажу связку с 1С и модель безопасности на короткой демонстрации. Когда удобно?</t>
+          <t>Могу коротко показать, как сервис связан с 1С и как устроена безопасность. 15 минут хватит. Когда вам удобно?</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="4" t="n"/>
     </row>
-    <row r="16" ht="86" customHeight="1">
+    <row r="16" ht="80" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Вопросы Смартвей</t>
@@ -916,26 +916,26 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Как сейчас организуете командировки? Как часто они у вас проходят? Кто этим занимается?</t>
+          <t>[ИО], а каким образом сейчас у вас организованы командировки? Как часто они проходят? Кто этим занимается?</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Как закрываете авансовые отчёты и попадают ли данные в 1С без ручного ввода? Сколько времени это отнимает?</t>
+          <t>А как закрываете авансовые отчёты? Данные сами попадают в 1С или всё вручную вводите? Сколько времени это занимает?</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>Кто оформляет приказы/служебные на командировки? Бывает ли путаница с датами и документами?</t>
+          <t>Кто у вас оформляет приказы и служебные на командировки? Бывает ли путаница с датами и документами?</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>Есть ли сейчас интеграция travel-сервиса с 1С / внутренними системами? Или всё сводите вручную?</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="100" customHeight="1">
+          <t>Есть ли сейчас связка travel-сервиса с вашей 1С, или всё сводите руками?</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="110" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Презентация Смартвей</t>
@@ -943,26 +943,26 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>«Смартвей» — сервис для командировок с глубокой интеграцией с 1С: заявка → согласование → билеты/отели → кадровые приказы и авансовые. Цены поставщиков без сервисных сборов, тревел-политики, аналитика. Бухгалтерии экономит до 4 рабочих дней в месяц. Контроль бюджета и согласования — у руководителя в одном окне.</t>
+          <t>Понял(а) вас. Есть сервис «Смартвей» — для планирования и организации командировок. Сотрудник выбирает направление и даты, система сравнивает цены и предлагает варианты. Можно бронировать билеты и отели без лишних комиссий. А главное — всё связано с вашей 1С: формируются приказы и авансовые отчёты. Вы видите согласования и бюджет в одном месте.</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>«Смартвей» — сервис для командировок с глубокой интеграцией с 1С: заявка → согласование → билеты/отели → кадровые приказы и авансовые. Цены поставщиков без сервисных сборов, тревел-политики, аналитика. Бухгалтерии экономит до 4 рабочих дней в месяц. Авансовые и закрывающие документы уходят в 1С без ручного набора.</t>
+          <t>Понял(а) вас. «Смартвей» помогает не только купить билет, но и закрыть документы. Авансовые уходят в 1С без ручного набора. Бухгалтерии это экономит до четырёх рабочих дней в месяц.</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Если командировки регулярные — «Смартвей» убирает хаос с приказами и документами поездок, данные стыкуются с ЗУП/1С.</t>
+          <t>Если командировки бывают регулярно, «Смартвей» помогает навести порядок с приказами и документами поездок. Данные стыкуются с вашей 1С / ЗУП.</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>«Смартвей» — сервис для командировок с глубокой интеграцией с 1С: заявка → согласование → билеты/отели → кадровые приказы и авансовые. Цены поставщиков без сервисных сборов, тревел-политики, аналитика. Бухгалтерии экономит до 4 рабочих дней в месяц. Есть API и синхронизация с 1С; реестр ПО Минцифры, требования по безопасности закрыты.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="52" customHeight="1">
+          <t>Понял(а) вас. «Смартвей» хорошо стыкуется с 1С, есть понятная схема подключения. Сервис в реестре Минцифры, по безопасности требования закрыты. Бухгалтерии это экономит до четырёх рабочих дней в месяц.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="55" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Передача коллеге</t>
@@ -970,22 +970,22 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Этим сервисом занимается другой мой коллега — передам ваш контакт, он свяжется в ближайшее время и покажет под ваш процесс.</t>
+          <t>Хорошо, спасибо вам за обратную связь! Этим сервисом занимается другой мой коллега, поэтому я передам ваш контакт — он в ближайшее время с вами свяжется и всё покажет.</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Этим сервисом занимается другой мой коллега — передам ваш контакт, он свяжется в ближайшее время и покажет под ваш процесс.</t>
+          <t>Хорошо, спасибо вам за обратную связь! Этим сервисом занимается другой мой коллега, поэтому я передам ваш контакт — он в ближайшее время с вами свяжется и всё покажет.</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Этим сервисом занимается другой мой коллега — передам ваш контакт, он свяжется в ближайшее время и покажет под ваш процесс.</t>
+          <t>Хорошо, спасибо вам за обратную связь! Этим сервисом занимается другой мой коллега, поэтому я передам ваш контакт — он в ближайшее время с вами свяжется и всё покажет.</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Этим сервисом занимается другой мой коллега — передам ваш контакт, он свяжется в ближайшее время и покажет под ваш процесс.</t>
+          <t>Хорошо, спасибо вам за обратную связь! Этим сервисом занимается другой мой коллега, поэтому я передам ваш контакт — он в ближайшее время с вами свяжется и всё покажет.</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       <c r="D19" s="4" t="n"/>
       <c r="E19" s="4" t="n"/>
     </row>
-    <row r="20" ht="64" customHeight="1">
+    <row r="20" ht="70" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Финиш</t>
@@ -1008,22 +1008,22 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Спасибо за время, [ИО]! Сверим контакты: направлю приглашение на демо / передам данные коллеге из Смартвей. Подтвердим связь на [день, время], верно? Отлично, тогда напишу/позвоню. Хорошего дня!</t>
+          <t>Спасибо вам за уделённое время, [ИО]! Давайте сверим контактные данные — туда я направлю приглашение на демонстрацию / передам данные коллеге из Смартвей. Подтвердим время связи: договорились повторно связаться [день, время], верно? Отлично, тогда я напишу или позвоню вам в это время. Хорошего дня!</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Спасибо за время, [ИО]! Сверим контакты: направлю приглашение на демо / передам данные коллеге из Смартвей. Подтвердим связь на [день, время], верно? Отлично, тогда напишу/позвоню. Хорошего дня!</t>
+          <t>Спасибо вам за уделённое время, [ИО]! Давайте сверим контактные данные — туда я направлю приглашение на демонстрацию / передам данные коллеге из Смартвей. Подтвердим время связи: договорились повторно связаться [день, время], верно? Отлично, тогда я напишу или позвоню вам в это время. Хорошего дня!</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>Спасибо за время, [ИО]! Сверим контакты: направлю приглашение на демо / передам данные коллеге из Смартвей. Подтвердим связь на [день, время], верно? Отлично, тогда напишу/позвоню. Хорошего дня!</t>
+          <t>Спасибо вам за уделённое время, [ИО]! Давайте сверим контактные данные — туда я направлю приглашение на демонстрацию / передам данные коллеге из Смартвей. Подтвердим время связи: договорились повторно связаться [день, время], верно? Отлично, тогда я напишу или позвоню вам в это время. Хорошего дня!</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>Спасибо за время, [ИО]! Сверим контакты: направлю приглашение на демо / передам данные коллеге из Смартвей. Подтвердим связь на [день, время], верно? Отлично, тогда напишу/позвоню. Хорошего дня!</t>
+          <t>Спасибо вам за уделённое время, [ИО]! Давайте сверим контактные данные — туда я направлю приглашение на демонстрацию / передам данные коллеге из Смартвей. Подтвердим время связи: договорились повторно связаться [день, время], верно? Отлично, тогда я напишу или позвоню вам в это время. Хорошего дня!</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
     <row r="22" ht="48" customHeight="1">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>• Порядок в звонке: ДОКИ → КабС → Смартвей. • Кадровику ДОКИ не продавливать. • В КабС обязательно: Госуслуги-аналогия, пилот на 1 отдел, &lt;30 ₽/чел, ст. 136/173, мягко про экологию. • В ДОКИ: ИТС ПРОФ + 3 мес безлимит + «попробуйте / не продлевать можно». • Узнать кол-во сотрудников до озвучки цены. • Возражения — на листе «Отработка возражений».</t>
+          <t>• Порядок: ДОКИ → КабС → Смартвей. • Кадровику ДОКИ не продавливать. • В КабС: «как Госуслуги», один отдел на старт, меньше 30 ₽/чел, ст. 136 и 173, про экологию — коротко. • В ДОКИ: ИТС ПРОФ, 3 месяца бесплатно, «попробуйте — можно не продлевать». • Перед ценой спросить, сколько сотрудников. • Возражения — на втором листе.</t>
         </is>
       </c>
       <c r="B22" s="14" t="n"/>
@@ -1082,7 +1082,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ОТРАБОТКА ВОЗРАЖЕНИЙ ДЛЯ МЕНЕДЖЕРА</t>
+          <t>ОТРАБОТКА ВОЗРАЖЕНИЙ</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1091,7 +1091,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Схема ответа: эмпатия → снятие страха → выгода / цифра / закон → следующий шаг (демо / пилот)</t>
+          <t>Как отвечать: сначала согласиться и понять → снять страх → коротко про пользу → предложить демо или пробный период</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>Отработка для менеджера</t>
+          <t>Что сказать клиенту</t>
         </is>
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
-          <t>На кого сильнее давит</t>
+          <t>Кому чаще</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Понимаю. Не предлагаю всё ломать. По ИТС ПРОФ у вас уже есть 3 месяца безлимита — просто попробуйте и сравните удобство. Можно работать из 1С или через веб без привязки. Не понравится — не продлеваете, обязательств нет.</t>
+          <t>Понимаю вас, привычный порядок — это спокойно. Я и не предлагаю всё менять. По ИТС ПРОФ у вас уже есть три месяца безлимита — можно просто попробовать и сравнить, удобно ли. Можно из 1С, можно через веб. Не понравится — не продлеваете, обязательств нет.</t>
         </is>
       </c>
       <c r="C5" s="18" t="inlineStr">
@@ -1141,7 +1141,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="54" customHeight="1">
+    <row r="6" ht="66" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
           <t>У нас уже Диадок / СБИС</t>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Отлично, вы уже в ЭДО. Вопрос в удобстве: многие работают через отдельный веб-кабинет. В ДОКИ кнопка «Отправить» прямо в 1С, либо веб — как удобнее. Давайте сравните на промопериоде без риска.</t>
+          <t>Отлично, значит, вы уже с ЭДО работаете. Часто неудобство в другом: приходится заходить в отдельный кабинет. В «ДОКИ» можно отправлять прямо из 1С — или через веб, как вам привычнее. Давайте просто сравните на бесплатном периоде, без риска.</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Всю настройку берём на себя. Интеграция типовая, для IT — минимальное участие. Промо на 3 месяца как раз чтобы оценить без проекта «на полгода».</t>
+          <t>Понимаю. Всю настройку мы берём на себя, ваших специалистов почти не отвлекаем. Три месяца как раз для того, чтобы спокойно посмотреть, нужно ли это вам.</t>
         </is>
       </c>
       <c r="C7" s="18" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Честно: после промо — только если вам удобно. Не понравится — можно не продлевать. Никаких скрытых обязательств в заходе нет.</t>
+          <t>Честно скажу: после пробного периода — только если вам действительно удобно. Не понравится — можно не продлевать. Ни к чему не обязывает.</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Согласен(на), ДОКИ больше про обмен с контрагентами. Тогда коротко отмечу для бухгалтерии/руководства и перейду к Кабинету сотрудника — он как раз ваш инструмент.</t>
+          <t>Согласен(на) с вами, «ДОКИ» больше про обмен с контрагентами. Тогда не буду вас этим загружать — лучше расскажу про Кабинет сотрудника. Он как раз про вашу работу.</t>
         </is>
       </c>
       <c r="C9" s="18" t="inlineStr">
@@ -1229,16 +1229,16 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>Отработка для менеджера</t>
+          <t>Что сказать клиенту</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>На кого сильнее давит</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="54" customHeight="1">
+          <t>Кому чаще</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="66" customHeight="1">
       <c r="A12" s="17" t="inlineStr">
         <is>
           <t>У нас всё на бумаге, нас устраивает</t>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Привычный порядок — это нормально. Сервис не ломает процесс: это дополнительный канал, «Госуслуги для сотрудников». Бумагу можно оставить, а рутину — постепенно убрать. Начните с одного отдела.</t>
+          <t>Понимаю, привычный порядок — это надёжно. Сервис ничего не ломает: это просто ещё один удобный канал, как Госуслуги для ваших сотрудников. Бумагу можно оставить, а часть рутины постепенно убрать. Можно начать с одного отдела.</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="66" customHeight="1">
+    <row r="13" ht="78" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
         <is>
           <t>Пока не обязательно — не будем</t>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>Именно поэтому сейчас комфортный момент: цифровизация уже идёт (ЭДО, ЭПД), КЭДО — следующий шаг. Ст. 136 уже обязывает по расчётным листкам; по ст. 173 и общей линии законодательства лучше подготовиться без спешки. Пилот на один отдел — без стресса.</t>
+          <t>Именно поэтому сейчас как раз спокойный момент. Цифровизация уже идёт — ЭДО, электронные документы, и кадровый электронный документооборот — следующий шаг. По статье 136 уже есть требования к расчётным листкам; по 173-й и общей линии законодательства лучше подготовиться без спешки. Начните с одного отдела — без напряжения.</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Как раз для небольших команд удобно: меньше 30 ₽ в месяц на сотрудника. За 10 человек — порядка 280–300 ₽/мес, как пара картриджей, но с экономией времени бухгалтера и кадров.</t>
+          <t>Как раз для небольших компаний это удобно: меньше 30 рублей в месяц на сотрудника. За 10 человек — порядка 280–300 рублей в месяц. Сопоставимо с картриджами, а времени у бухгалтера и кадров экономит заметно.</t>
         </is>
       </c>
       <c r="C14" s="18" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>Ориентир 21–30 ₽/мес за сотрудника. Для мягкого входа — один отдел за низкую стоимость, потом масштабирование. Считаем на ваш штат и сравниваем с бумагой, печатью и потерянным временем.</t>
+          <t>Стоимость — от 21 до 30 рублей в месяц за сотрудника. Можно начать с одного отдела за небольшие деньги и потом расширить. Давайте посчитаем на ваш штат — часто выходит меньше, чем кажется.</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Интерфейс проще многих привычных приложений — логика как у Госуслуг: посмотрел, подал, подписал. Можно идти поэтапно (сначала расчётки или отпуска). Обучение короткое, видеоуроки есть; часть сотрудников работает с браузера.</t>
+          <t>Понимаю опасение. Сервис сделан проще многих привычных приложений — логика как у Госуслуг: посмотрел, подал, подписал. Можно начать с малого — например, только с расчёток или отпусков. Обучение короткое, есть видео. Часть сотрудников работает прямо из браузера.</t>
         </is>
       </c>
       <c r="C16" s="18" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>Настраиваем мы. Сервис уже связан с вашей 1С — IT не тянет тяжёлый проект. Вам — пилот на небольшой контур и 15 минут демо, чтобы увидеть эффект.</t>
+          <t>Мы всё настраиваем сами. Сервис уже связан с вашей 1С — тяжёлого проекта для IT нет. Вам достаточно посмотреть 15-минутную демонстрацию и начать с небольшого отдела.</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -1345,15 +1345,15 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="54" customHeight="1">
+    <row r="18" ht="66" customHeight="1">
       <c r="A18" s="17" t="inlineStr">
         <is>
-          <t>Есть кадровик/бухгалтер — и так справляется</t>
+          <t>Есть кадровик / бухгалтер, он всё делает</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>И не заменяем специалиста. Убираем рутину: перенос с бумаги, печать, раздача листков, «где моя справка?». Сотрудник сам подаёт — кадровик утверждает. Меньше ошибок и авралов.</t>
+          <t>И это хорошо. Сервис не заменяет специалиста — он убирает рутину: перенос с бумаги, печать, раздачу листков, вопросы «где моя справка?». Сотрудник сам подаёт заявление, а вы только утверждаете. Меньше ошибок и беготни.</t>
         </is>
       </c>
       <c r="C18" s="18" t="inlineStr">
@@ -1363,15 +1363,15 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="54" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>Не хотим электронную подпись</t>
+          <t>Мы не хотим электронную подпись</t>
         </is>
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>УНЭП в сервисе — для внутренних кадровых документов, юридически значимо. Это не замена вашей основной ЭП. Можно подписывать и через Госключ. Для пилота часто начинают с расчётных листков и заявлений.</t>
+          <t>Понимаю. Подпись в сервисе нужна только для внутренних кадровых документов и имеет юридическую силу. Это не замена вашей основной подписи. Можно подписывать и через Госключ. На старте часто начинают просто с расчётных листков и заявлений.</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -1382,15 +1382,15 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="54" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>Расчётки выдаём на руки — привыкли</t>
+          <t>Расчётные листки выдаём на руки, привыкли</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Можно оставить бумагу как доп. канал. Но ст. 136 требует извещения — в кабинете есть фиксация ознакомления. При проверке не нужно искать бумажную подпись Иванова за прошлый год.</t>
+          <t>Понимаю. Бумажную выдачу можно оставить. Но по статье 136 нужно извещать сотрудников о зарплате — в кабинете это делается быстро, и видно, что человек ознакомился. При проверке не придётся искать бумажную подпись за прошлый год.</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
@@ -1402,12 +1402,12 @@
     <row r="21" ht="54" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>Нет удалённых сотрудников</t>
+          <t>У нас нет удалённых сотрудников</t>
         </is>
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>Сервис полезен и в офисе: меньше беготни, прозрачные статусы, меньше потерянных заявлений. Согласование со смартфона руководителю — часы вместо дней.</t>
+          <t>Сервис полезен и в офисе: меньше беготни по кабинетам, заявления не теряются, руководитель может согласовать со смартфона. Часто вместо дней получается несколько часов.</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -1417,15 +1417,15 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="54" customHeight="1">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" s="17" t="inlineStr">
         <is>
-          <t>Уже другой КЭДО</t>
+          <t>Мы уже используем другой сервис для КЭДО</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Тогда вы уже понимаете ценность цифры. Наше преимущество — родная связка с 1С: документы в вашей базе, заявления сразу в ЗУП/1С. Предлагаю сравнить на 15-минутном демо.</t>
+          <t>Отлично, значит, вы уже оценили, как удобнее в цифре. Наше преимущество — тесная связь с вашей 1С: документы в вашей базе, заявления сразу попадают в программу. Предлагаю просто сравнить на демонстрации — это займёт 15 минут.</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">
@@ -1439,12 +1439,12 @@
     <row r="23" ht="54" customHeight="1">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>Безопасность / персданные</t>
+          <t>Вопрос безопасности / персданные</t>
         </is>
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>Документы хранятся в вашей базе 1С. ЦОД 1С — аттестаты ФСТЭК, есть локальная версия. Персданные не нужно гонять по мессенджерам — как раз снижает риски и штрафы.</t>
+          <t>Документы хранятся в вашей базе 1С. Дата-центр 1С — с аттестатами ФСТЭК, есть локальная версия. Персональные данные не нужно отправлять в мессенджерах — как раз меньше рисков и спокойнее при проверках.</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -1454,15 +1454,15 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="42" customHeight="1">
+    <row r="24" ht="54" customHeight="1">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>Трудно из‑за доп. документации на КЭДО</t>
+          <t>Трудно из‑за дополнительной документации на КЭДО</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Мы даём шаблоны: положение о КЭДО, уведомление, согласие/отказ, заявление на УНЭП. Переход делаем управляемым: один отдел → вся компания.</t>
+          <t>Понимаю. Мы даём готовые шаблоны: положение о КЭДО, уведомление, согласие или отказ, заявление на подпись. И сам переход делаем спокойно: сначала один отдел, потом вся компания.</t>
         </is>
       </c>
       <c r="C24" s="18" t="inlineStr">
@@ -1472,15 +1472,15 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="54" customHeight="1">
+    <row r="25" ht="66" customHeight="1">
       <c r="A25" s="19" t="inlineStr">
         <is>
-          <t>Сотрудники всё равно будут писать в бухгалтерию напрямую</t>
+          <t>Сотрудники всё равно будут писать напрямую</t>
         </is>
       </c>
       <c r="B25" s="20" t="inlineStr">
         <is>
-          <t>Часть так и делает первое время — это нормально. Когда видят остаток отпуска, справки и статусы в кабинете — обращений становится меньше. Кадровик перестаёт быть «справочным бюро».</t>
+          <t>Первое время часть так и делает — это нормально. Когда человек видит в кабинете остаток отпуска, справки и статус заявления — таких обращений обычно становится меньше. Вам меньше приходится быть «справочным бюро».</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -1507,16 +1507,16 @@
       </c>
       <c r="B27" s="16" t="inlineStr">
         <is>
-          <t>Отработка для менеджера</t>
+          <t>Что сказать клиенту</t>
         </is>
       </c>
       <c r="C27" s="16" t="inlineStr">
         <is>
-          <t>На кого сильнее давит</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="66" customHeight="1">
+          <t>Кому чаще</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="78" customHeight="1">
       <c r="A28" s="17" t="inlineStr">
         <is>
           <t>Командировок мало / редко</t>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Тогда зафиксирую: если поездок почти нет — сервис не приоритет. Если бывают всплески (выставки, филиалы, сервис) — даже редкие поездки без единого процесса съедают время бухгалтерии. Могу передать коллеге коротко — он скажет, есть ли смысл.</t>
+          <t>Хорошо, спасибо. Если поездок почти нет — сервис может быть не самым нужным. Если иногда бывают всплески — выставки, филиалы, выездной сервис — даже редкие командировки часто отнимают много времени у бухгалтерии. Могу коротко передать коллеге — он подскажет, есть ли смысл смотреть.</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
@@ -1534,7 +1534,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="54" customHeight="1">
+    <row r="29" ht="66" customHeight="1">
       <c r="A29" s="19" t="inlineStr">
         <is>
           <t>Уже работаем с агентством / другим сервисом</t>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>Ок. Часто боль не в «купить билет», а в связке с 1С: приказы, авансовые, ручной ввод. Смартвей как раз про закрытие контура до документов в 1С. Коллега сравнит ваш текущий процесс без давления.</t>
+          <t>Понял(а) вас. Часто неудобство не в покупке билета, а дальше: приказы, авансовые, ручной ввод в 1С. «Смартвей» как раз помогает закрыть это до документов в программе. Коллега сравнит с вашим текущим процессом, без давления.</t>
         </is>
       </c>
       <c r="C29" s="21" t="inlineStr">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="54" customHeight="1">
+    <row r="30" ht="66" customHeight="1">
       <c r="A30" s="17" t="inlineStr">
         <is>
           <t>Дорого / абонентка</t>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Модель обычно за месяцы, когда есть поездки; есть постоплата. Считают экономию на перерасходе и на времени бухгалтерии (до 4 дней в месяц). Точные условия озвучит профильный менеджер.</t>
+          <t>Обычно платят за те месяцы, когда есть поездки; есть постоплата. Считают экономию на перерасходе и на времени бухгалтерии — до четырёх дней в месяц. Точные условия лучше озвучит коллега, который этим занимается.</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
@@ -1570,7 +1570,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="54" customHeight="1">
+    <row r="31" ht="66" customHeight="1">
       <c r="A31" s="19" t="inlineStr">
         <is>
           <t>Не хочу ещё один сервис</t>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B31" s="20" t="inlineStr">
         <is>
-          <t>Понимаю. Здесь как раз идея «одно окно»: заявка, согласование, билеты, отчётность и выгрузка в 1С — меньше таблиц и мессенджеров. Я не продаю в лоб — передам коллеге, он покажет под ваш сценарий.</t>
+          <t>Понимаю вас. Здесь идея как раз в том, чтобы было одно место: заявка, согласование, билеты, отчёты и выгрузка в 1С — меньше таблиц и переписок. Я не буду вас уговаривать — передам коллеге, он покажет на вашем примере.</t>
         </is>
       </c>
       <c r="C31" s="21" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Интеграции с 1С у Смартвей отработанные; для IT обычно понятный контур. Коллега придёт уже с схемой подключения и ответами по безопасности (реестр ПО Минцифры и др.).</t>
+          <t>Понимаю. У «Смартвей» подключение к 1С уже отработанное, для IT обычно всё понятно. Коллега придёт со схемой и ответами по безопасности — в том числе по реестру Минцифры.</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
@@ -1608,7 +1608,7 @@
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>4) ТОЧКИ ДАВЛЕНИЯ ПО ЛПР (шпаргалка)</t>
+          <t>4) ШПАРГАЛКА ПО ЛПР</t>
         </is>
       </c>
       <c r="B33" s="15" t="n"/>
@@ -1617,12 +1617,12 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="16" t="inlineStr">
         <is>
-          <t>ЛПР</t>
+          <t>С кем говорим</t>
         </is>
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>Что усиливать в разговоре</t>
+          <t>На что опираться</t>
         </is>
       </c>
       <c r="C34" s="16" t="inlineStr">
@@ -1631,7 +1631,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="42" customHeight="1">
+    <row r="35" ht="54" customHeight="1">
       <c r="A35" s="22" t="inlineStr">
         <is>
           <t>Руководитель</t>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Скорость согласований, контроль, меньше штрафов и хаоса, пилот на 1 отдел, готовность к обязательности КЭДО, бюджет командировок.</t>
+          <t>Быстрые согласования, контроль, меньше штрафов и хаоса. Старт с одного отдела. Подготовиться к КЭДО заранее. Порядок в командировках и бюджете.</t>
         </is>
       </c>
       <c r="C35" s="23" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>Ст. 136 и расчётные листки с ознакомлением, меньше ручного ввода, тайность ЗП, авансовые из Смартвей в 1С, ЭДО из 1С без веб-кабинета.</t>
+          <t>Статья 136 и расчётные листки с ознакомлением. Меньше ручного ввода. Авансовые из Смартвей в 1С. ЭДО прямо из 1С, без лишнего кабинета.</t>
         </is>
       </c>
       <c r="C36" s="21" t="inlineStr">
@@ -1665,7 +1665,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="42" customHeight="1">
+    <row r="37" ht="54" customHeight="1">
       <c r="A37" s="22" t="inlineStr">
         <is>
           <t>Кадровик</t>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Самообслуживание сотрудников (как Госуслуги), заявления→приказы в 1С, меньше «где справка?», удалёнка, архив, шаблоны перехода на КЭДО.</t>
+          <t>Как Госуслуги для сотрудников: сами подают и смотрят. Заявления сразу в 1С. Меньше вопросов «где справка?». Удалёнка. Готовые шаблоны для перехода.</t>
         </is>
       </c>
       <c r="C37" s="23" t="inlineStr">
@@ -1682,7 +1682,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="42" customHeight="1">
+    <row r="38" ht="54" customHeight="1">
       <c r="A38" s="19" t="inlineStr">
         <is>
           <t>IT-специалист</t>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>Встройка в 1С, хранение в базе клиента, ФСТЭК/локальная версия, минимальная нагрузка на внедрение, API/безопасность Смартвей.</t>
+          <t>Уже связано с 1С. Документы в базе клиента. ФСТЭК / локальная версия. Настройку берём на себя. По Смартвей — понячное подключение и безопасность.</t>
         </is>
       </c>
       <c r="C38" s="21" t="inlineStr">

--- a/скрипт КабС, ДОКИ, Смартвей.xlsx
+++ b/скрипт КабС, ДОКИ, Смартвей.xlsx
@@ -9,9 +9,11 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Скрипт" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Отработка возражений" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Скрипт КОРП" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Скрипт'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Скрипт КОРП'!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -74,7 +76,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -126,6 +128,11 @@
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDECEC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -153,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -223,6 +230,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1710,4 +1723,775 @@
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>СКРИПТ ДЛЯ КОРПОРАТИВНОГО СЕГМЕНТА: «ДОКИ» → «1С:КАБИНЕТ СОТРУДНИКА» → «СМАРТВЕЙ»</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Компании от 100 млн ₽ · длинный цикл согласования · больше кабинетов · преддемо не на звонке: письмо на почту + заранее согласованная встреча и состав</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>ЭТАП</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>РУКОВОДИТЕЛЬ</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>БУХГАЛТЕР</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>КАДРОВИК</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>IT-СПЕЦИАЛИСТ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>0. ЧЕМ КОРП ОТЛИЧАЕТСЯ ОТ ОБЫЧНОЙ ПРОДАЖИ (шпаргалка менеджеру)</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="95" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Логика корп</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>В корпе звонок — это не продажа и не презентация. Задача звонка: понять роль, нащупать интерес, согласовать состав и время встречи, отправить материалы на почту. Полную презентацию и «преддемо» на бегу с бухгалтером не делаем — иначе не соберём нужных ЛПР и потеряем сделку на длинном согласовании. Пилот обычно больше 10 кабинетов: отдел / филиал / 50–100+ сотрудников. Счёт — после встречи, демо со специалистом и внутреннего согласования у клиента.</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>В корпе звонок — это не продажа и не презентация. Задача звонка: понять роль, нащупать интерес, согласовать состав и время встречи, отправить материалы на почту. Полную презентацию и «преддемо» на бегу с бухгалтером не делаем — иначе не соберём нужных ЛПР и потеряем сделку на длинном согласовании. Пилот обычно больше 10 кабинетов: отдел / филиал / 50–100+ сотрудников. Счёт — после встречи, демо со специалистом и внутреннего согласования у клиента.</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>В корпе звонок — это не продажа и не презентация. Задача звонка: понять роль, нащупать интерес, согласовать состав и время встречи, отправить материалы на почту. Полную презентацию и «преддемо» на бегу с бухгалтером не делаем — иначе не соберём нужных ЛПР и потеряем сделку на длинном согласовании. Пилот обычно больше 10 кабинетов: отдел / филиал / 50–100+ сотрудников. Счёт — после встречи, демо со специалистом и внутреннего согласования у клиента.</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>В корпе звонок — это не продажа и не презентация. Задача звонка: понять роль, нащупать интерес, согласовать состав и время встречи, отправить материалы на почту. Полную презентацию и «преддемо» на бегу с бухгалтером не делаем — иначе не соберём нужных ЛПР и потеряем сделку на длинном согласовании. Пилот обычно больше 10 кабинетов: отдел / филиал / 50–100+ сотрудников. Счёт — после встречи, демо со специалистом и внутреннего согласования у клиента.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>1. ПРИВЕТСТВИЕ И КВАЛИФИКАЦИЯ (короткий звонок)</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+    </row>
+    <row r="7" ht="78" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Приветствие</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Добрый день, [ИО]! Компания «[название]», верно? Меня зовут [имя], я из «Форуса» — мы ваш партнёр по 1С. Звоню ненадолго: у нас есть сервисы по электронному документообороту с сотрудниками и контрагентами. Подскажите, пожалуйста, удобно ли сейчас буквально 3–4 минуты, чтобы понять, кому из коллег это будет полезно, и договориться о короткой встрече?</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Добрый день, [ИО]! Компания «[название]», верно? Меня зовут [имя], я из «Форуса» — мы ваш партнёр по 1С. Звоню ненадолго: у нас есть сервисы по электронному документообороту с сотрудниками и контрагентами. Подскажите, пожалуйста, удобно ли сейчас буквально 3–4 минуты, чтобы понять, кому из коллег это будет полезно, и договориться о короткой встрече?</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Добрый день, [ИО]! Компания «[название]», верно? Меня зовут [имя], я из «Форуса» — мы ваш партнёр по 1С. Звоню ненадолго: у нас есть сервисы по электронному документообороту с сотрудниками и контрагентами. Подскажите, пожалуйста, удобно ли сейчас буквально 3–4 минуты, чтобы понять, кому из коллег это будет полезно, и договориться о короткой встрече?</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Добрый день, [ИО]! Компания «[название]», верно? Меня зовут [имя], я из «Форуса» — мы ваш партнёр по 1С. Звоню ненадолго: у нас есть сервисы по электронному документообороту с сотрудниками и контрагентами. Подскажите, пожалуйста, удобно ли сейчас буквально 3–4 минуты, чтобы понять, кому из коллег это будет полезно, и договориться о короткой встрече?</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="110" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Квалификация</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Подскажите, вы скорее курируете решения по персоналу и процессам в целом? Сколько примерно сотрудников в компании / группе? Есть ли филиалы или удалённый персонал? Кто обычно принимает решение по таким сервисам — вы, финансовый блок, кадры, IT?</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Подскажите, вы главный бухгалтер / руководитель расчётного блока? Сколько roughly сотрудников на расчёте? Работаете в 1С:ЗУП / ERP? По таким темам вы сами смотрите или подключаете кадры и IT?</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Подскажите, вы руководите кадровой службой / ОКП? Какой примерно штат и как сейчас устроен обмен документами с сотрудниками? Кого ещё важно подключить, если будем смотреть кадровый электронный документооборот?</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Подскажите, вы отвечаете за 1С / информационную безопасность / инфраструктуру? Какой контур 1С сейчас: ЗУП, ERP, несколько баз? По новым сервисам кто ещё должен быть на встрече — кадры, бухгалтерия, ИБ?</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2. ДОКИ — коротко на звонке, детали — на почту и встречу</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+    </row>
+    <row r="10" ht="85" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Заход ДОКИ</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>[ИО], по ИТС ПРОФ у вас доступно бесплатное подключение «ДОКИ» на три месяца с безлимитным обменом документов. В крупных компаниях это обычно смотрят вместе с бухгалтерией и IT — не в формате «сейчас на телефоне», а на встрече. Могу коротко уточнить текущую схему и прислать описание на почту.</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>[ИО], по ИТС ПРОФ у вас доступно бесплатное подключение «ДОКИ» на три месяца с безлимитным обменом документов. В крупных компаниях это обычно смотрят вместе с бухгалтерией и IT — не в формате «сейчас на телефоне», а на встрече. Могу коротко уточнить текущую схему и прислать описание на почту.</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>[ИО], «ДОКИ» — это скорее про обмен с контрагентами, не про кадры. Если для бухгалтерии актуально — отмечу и пришлю материалы. Для вас важнее будет Кабинет сотрудника — его как раз и вынесем на встречу.</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>[ИО], по ИТС ПРОФ у вас доступно бесплатное подключение «ДОКИ» на три месяца с безлимитным обменом документов. В крупных компаниях это обычно смотрят вместе с бухгалтерией и IT — не в формате «сейчас на телефоне», а на встрече. Могу коротко уточнить текущую схему и прислать описание на почту.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="95" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Вопросы ДОКИ</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Как сейчас обмениваетесь документами с контрагентами — несколько операторов ЭДО или единый контур? Есть ли требование, чтобы всё шло из 1С, без отдельных кабинетов?</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Работаете из 1С или через веб-кабинеты операторов? Насколько для вас критичен единый контур и нагрузка на бухгалтерию при больших объёмах?</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Для кадровика: «Хорошо, ДОКИ оставим для бухгалтерии. На встрече сфокусируемся на Кабинете сотрудника».</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Как сейчас устроена интеграция ЭДО с вашими базами 1С? Нужна ли будет оценка со стороны IT/ИБ, если подключим «ДОКИ» в контур?</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="95" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Презентация ДОКИ</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Коротко: «1С:ДОКИ» — ЭДО от 1С и «Калуга Астрал». Можно встроить в вашу 1С или работать через веб. По ИТС ПРОФ — три месяца безлимита, можно попробовать и не продлевать. В корпе детали и схему подключения лучше разобрать на встрече с бухгалтерией и IT. Я пришлю описание на почту — без обязательств.</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>Коротко: «1С:ДОКИ» — ЭДО от 1С и «Калуга Астрал». Можно встроить в вашу 1С или работать через веб. По ИТС ПРОФ — три месяца безлимита, можно попробовать и не продлевать. В корпе детали и схему подключения лучше разобрать на встрече с бухгалтерией и IT. Я пришлю описание на почту — без обязательств.</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Кратко: «Это для контрагентов. Материалы бухгалтеру отправлю. На встрече разберём сервис для кадров».</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>Коротко: «1С:ДОКИ» — ЭДО от 1С и «Калуга Астрал». Можно встроить в вашу 1С или работать через веб. По ИТС ПРОФ — три месяца безлимита, можно попробовать и не продлевать. В корпе детали и схему подключения лучше разобрать на встрече с бухгалтерией и IT. Я пришлю описание на почту — без обязательств.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>3. 1С:КАБИНЕТ СОТРУДНИКА — сбор потребности на звонке (без полной презентации)</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+    </row>
+    <row r="14" ht="125" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Вопросы КабС</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Как сейчас у вас в компании устроен кадровый документооборот в масштабе — филиалы, удалёнка, согласования между подразделениями? Уже смотрели КЭДО или это пока на бумаге / в разрозненных инструментах? Если пилот — с какого контура логичнее начать: один филиал, одно юрлицо, один блок?</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Как сейчас массово выдаёте расчётные листки и фиксируете ознакомление по ст. 136? При проверках быстро находите подтверждения? Насколько расчётный блок перегружен рутиной на большом штате?</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Как сотрудники подают заявления и запрашивают справки при штате в сотни человек? Где узкое место: график отпусков, приём, удалённые сотрудники, архив? Какой отдел или филиал можно было бы взять в пилот?</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>Документы кадров где хранятся и как стыкуются с 1С:ЗУП / ERP? Какие требования ИБ к облаку, локальной версии, ФСТЭК? Сколько примерно контуров/баз нужно будет учесть при внедрении?</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="120" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Тизер КабС
+(не презентация)</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Не буду сейчас читать вам всю презентацию по телефону — в корпоративном формате это лучше сделать на встрече с нужным составом. Суть коротко: «1С:Кабинет сотрудника» — как Госуслуги для сотрудников, но внутри вашей 1С. Для крупных компаний обычно идём поэтапно: пилот на отдел или филиал, потом масштабирование. Стоимость на человека небольшая, эффект — на объёме. Детали, экономику и план внедрения пришлю на почту и разберём на встрече.</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>На большом штате главная история — расчётные листки с ознакомлением и меньше ручного труда. Полностью сервис показывать сейчас не буду: пришлю материалы и предложу встречу, где будем с цифрами и сценариями под ваш контур.</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>Для кадров это снятие потока однотипных обращений и заявления сразу в 1С. В корпе важно не «подключить всех завтра», а выбрать пилотный контур. Давайте согласуем встречу и состав — так будет предметнее.</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>Для IT важны контур, безопасность и нагрузка на внедрение. Это как раз вопросы не для телефонной презентации. Пришлю описание архитектуры и предложу встречу с участием кадров/бухгалтерии.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="110" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Коммерческий
+акцент КОРП</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>В корпоративном сегменте мы не предлагаем «подключить всех завтра». Обычно: пилот на филиал / юрлицо / 50–100+ кабинетов → оценка → тираж. Согласование у вас может занять время — поэтому лучше заранее заложить этапы и подключить всех, кто влияет на решение.</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Ориентир по цене — от 21–30 ₽/мес за кабинет, на объёме считается отдельно. Для старта важнее согласовать пилотный контур и экономику на ваш штат — подготовлю расчёт к встрече.</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Пилот лучше брать не «10 человек для галочки», а реальный отдел или филиал, чтобы кадры увидели эффект на потоке. Шаблоны документов перехода на КЭДО дадим.</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>Внедрение планируем как проект: доступы, ИБ, тестовый контур, обучение ключевых пользователей. На встрече покажем схему — без сюрпризов для IT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>4. ГЛАВНОЕ ОТЛИЧИЕ КОРП: ПОЧТА + ВСТРЕЧА (преддемо на звонке с бухгалтером НЕ делаем)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="130" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Договорённость
+о встрече</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Предлагаю не углубляться сейчас, а провести короткую рабочую встречу на 30–40 минут. На ней покажем логику сервиса и возможный пилот под ваш масштаб. Подскажите, кого важно пригласить с вашей стороны — финансы, кадры, IT, возможно ИБ или юридический блок? Какие дни на следующей неделе вам удобны?</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Полную презентацию на этом звонке проводить не буду — в вашем формате это обычно требует участия кадров и иногда IT. Давайте согласуем встречу: я пришлю материалы на почту заранее, чтобы вы могли посмотреть и позвать нужных коллег. Когда удобнее — на этой неделе или на следующей?</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Чтобы встреча была полезной, хорошо бы участие кадровой службы и того, кто согласовывает такие проекты. Могу провести встречу онлайн. Подскажите удобные слоты и почту, куда направить Reminder и материалы.</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Для IT как раз удобнее не телефонный разбор, а встреча с повесткой: архитектура, безопасность, этапы. Пришлю материалы заранее. Кого ещё подключить — кадры и бухгалтерию? Когда у вас есть окно на 30–40 минут?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="125" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Что отправить
+на почту</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>После звонка обязательно письмо: краткая цель встречи, предлагаемые дата/время, рекомендуемый состав участников, презентация / одностраничник по Кабинету сотрудника, при необходимости — блок про ДОКИ и вопросник «что уточнить до встречи». Тема письма понятная: «Материалы к встрече по 1С:Кабинет сотрудника — [Компания]».</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>В письме бухгалтеру: зачем встреча, кто желателен в составе, коротко про расчётные листки и пилот, вложение с описанием сервиса, просьба подтвердить слот или предложить другой.</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>В письме кадровику: фокус на заявлениях, отпусках, пилотном отделе/филиале, просьба позвать руководителя СУП / того, кто принимает решение. Без давления — «чтобы встреча прошла предметно».</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>В письме IT: архитектура/контур 1С, хранение в базе клиента, ФСТЭК/локальная версия, повестка встречи, просьба подтвердить участие ИБ при необходимости.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="100" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Состав встречи
+(регулятор)</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Минимум: ЛПР по процессу + кадры или финансы. Идеально: руководитель / HR / главный бухгалтер или расчётный блок / IT. Если решения идут через комитет — заранее спросить, кто готовит материалы внутрь.</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Бухгалтера одного на «преддемо в звонке» недостаточно для корп-сделки. Просим его помочь собрать состав и подтвердить время — он часто проводник, но не единственный ЛПР.</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Кадровик — ключевой пользователь. На встрече нужен тот, кто влияет на выбор пилотного контура.</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>IT нужен не всегда на первом тизере, но на корп-встрече лучше сразу, чтобы не получить стоп после «нам понравилось, но ИБ не пустит».</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>5. СКРИПТ ВСТРЕЧИ / ПРЕДДЕМО (уже не звонок) — сбор потребности → презентация → следующий шаг</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="95" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Старт встречи</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Спасибо, что выделили время. Цель встречи на 30–40 минут: уточнить, как у вас устроены процессы, коротко показать «1С:Кабинет сотрудника» и понять, имеет ли смысл пилот на выбранном контуре. В конце зафиксируем следующий шаг — демо со специалистом или подготовка коммерческого предложения.</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Сфокусируемся на расчётных листках, нагрузке расчётного блока и том, как выглядит пилот без ломки текущих процессов.</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Сфокусируемся на заявлениях, отпусках, самообслуживании сотрудников и пилотном контуре для кадров.</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Сфокусируемся на контуре 1С, безопасности, этапах внедрения и роли IT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="115" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>Глубокий сбор
+потребности</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Где сейчас теряется время и управляемость: согласования, филиалы, удалёнка, проверки? Кто внутри будет спонсором проекта? Какой горизонт решения — этот квартал, полугодие? Пилот: какой филиал/юрлицо/численность реалистичны?</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Как закрываете ст. 136 на всём штате? Сколько времени уходит на расчётки, справки, уточнения? Что будет критерием успеха пилота для финансового блока?</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>Сколько обращений «где справка / сколько дней отпуска» в неделю? Как работаете с удалёнными и с приёмом? Какой отдел готов быть пилотным и почему?</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>Какие требования к хранению данных и доступу? Сколько баз/контуров? Нужны ли анкета ИБ, тестовый контур, согласование службы безопасности?</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="115" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>Презентация
+на встрече</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>Показываем логику: сотрудник работает как в Госуслугах — заявления, документы, статусы. Для компании — прозрачные согласования и готовность к КЭДО без аврала. Акцент на масштабе: пилот → тираж, единые правила, меньше бумаги и хаоса между филиалами. Экологию упоминаем коротко. Дальше — дорожная карта и роль каждого блока.</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Акцент: расчётные листки с ознакомлением, меньше ручного труда, данные в 1С, понятная экономика на объёме. Не обещаем «внедрим за день» — показываем этапы.</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>Акцент: самообслуживание, заявления в 1С, пилотный отдел/филиал, шаблоны документов перехода, снижение потока однотипных вопросов.</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>Акцент: хранение в базе клиента, ФСТЭК/локальная версия, этапы внедрения, минимальная нагрузка на IT при поддержке Форус, стыковка с ЗУП/ERP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="110" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Закрытие встречи
+(не сразу счёт)</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>В корпе редко закрываем счёт в тот же день — и это нормально. Фиксируем: состав пилота (численность/контур), кто готовит внутреннее согласование, нужно ли демо со специалистом, срок обратной связи. Следующий шаг: демо и/или коммерческое предложение на пилот.</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Предлагаю следующий шаг — демонстрация со специалистом на ваших сценариях расчёток и после этого КП на пилотный контур. Вам так комфортно?</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Предлагаю демо на кадровых сценариях и параллельно наметить пилотный отдел. После демо подготовим КП и план обучения.</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Предлагаю техническое демо / ответы на вопросы ИБ и затем пилотную оценку по контурам. Какие документы от нас нужны для внутреннего согласования?</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>6. СМАРТВЕЙ — в корпе тоже через квалификацию и передачу, без продажи «сходу»</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+    </row>
+    <row r="27" ht="90" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>Вопросы Смартвей</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>Есть ли регулярные командировки по филиалам / объектам? Как сейчас устроен travel: агентство, несколько сервисов, вручную? Кто владелец процесса — административный блок, финансы?</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Как закрываете авансовые на объёме? Данные доходят до 1С без ручного ввода? Насколько это узкое место?</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>Кто оформляет кадровые документы по командировкам при большом потоке?</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>Нужна ли интеграция travel с 1С / внутренними системами и согласование ИБ?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="95" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>Презентация
+Смартвей</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>Если командировки регулярные и их много — имеет смысл отдельный разбор. «Смартвей» как раз про единое окно и связку с 1С. В корпе это обычно отдельная встреча с профильным менеджером — я передам контакт и контекст.</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>Для бухгалтерии ценность — авансовые и меньше ручного ввода в 1С. Детали и расчёт лучше даст коллега на отдельном созвоне.</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>Если поток командировок большой — кадровые документы тоже страдают. Могу передать коллеге, чтобы показали стыковку с ЗУП.</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>По интеграциям и безопасности коллега подготовит схему. Я передам ваш контакт и состав вопросов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="55" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Передача коллеге</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Этим блоком занимается отдельный коллега. Я передам ваш контакт, кратко опишу масштаб и текущую схему — он предложит удобный формат встречи. Без спама и давления.</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Этим блоком занимается отдельный коллега. Я передам ваш контакт, кратко опишу масштаб и текущую схему — он предложит удобный формат встречи. Без спама и давления.</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Этим блоком занимается отдельный коллега. Я передам ваш контакт, кратко опишу масштаб и текущую схему — он предложит удобный формат встречи. Без спама и давления.</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Этим блоком занимается отдельный коллега. Я передам ваш контакт, кратко опишу масштаб и текущую схему — он предложит удобный формат встречи. Без спама и давления.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>7. ЗАВЕРШЕНИЕ ЗВОНКА (корп)</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+    </row>
+    <row r="31" ht="85" customHeight="1">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>Финиш звонка</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>Спасибо вам за время, [ИО]! Зафиксируем: я направляю материалы на почту [e-mail], встреча [дата/время], состав [роли]. Если нужно перенести или добавить участника — просто ответьте на письмо. После встречи предложим следующий шаг: демо со специалистом и проработку пилота. Хорошего дня!</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Спасибо вам за время, [ИО]! Зафиксируем: я направляю материалы на почту [e-mail], встреча [дата/время], состав [роли]. Если нужно перенести или добавить участника — просто ответьте на письмо. После встречи предложим следующий шаг: демо со специалистом и проработку пилота. Хорошего дня!</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>Спасибо вам за время, [ИО]! Зафиксируем: я направляю материалы на почту [e-mail], встреча [дата/время], состав [роли]. Если нужно перенести или добавить участника — просто ответьте на письмо. После встречи предложим следующий шаг: демо со специалистом и проработку пилота. Хорошего дня!</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>Спасибо вам за время, [ИО]! Зафиксируем: я направляю материалы на почту [e-mail], встреча [дата/время], состав [роли]. Если нужно перенести или добавить участника — просто ответьте на письмо. После встречи предложим следующий шаг: демо со специалистом и проработку пилота. Хорошего дня!</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>ПАМЯТКА И ЧАСТЫЕ ВОЗРАЖЕНИЯ В КОРПЕ</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="n"/>
+      <c r="C32" s="13" t="n"/>
+      <c r="D32" s="13" t="n"/>
+      <c r="E32" s="13" t="n"/>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>• Звонок ≠ презентация. • Письмо на почту обязательно в день звонка. • Состав встречи согласуем заранее. • Пилот считаем от реального контура (отдел/филиал/50–100+), не «10 для галочки». • Счёт — после встречи/демо и внутреннего согласования. • Ведём статус: интересант → встреча → демо → КП → согласование → пилот.</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="n"/>
+      <c r="C33" s="14" t="n"/>
+      <c r="D33" s="14" t="n"/>
+      <c r="E33" s="14" t="n"/>
+    </row>
+    <row r="34" ht="110" customHeight="1">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Возражения
+корп</t>
+        </is>
+      </c>
+      <c r="B34" s="25" t="inlineStr">
+        <is>
+          <t>«Пришлите на почту» → «Конечно, так и планировал(а). Чтобы письмо было полезным — подтвердите почту и кого ещё копировать. И давайте сразу наметим слот встречи, пока материалы свежие».</t>
+        </is>
+      </c>
+      <c r="C34" s="25" t="inlineStr">
+        <is>
+          <t>«Мне нужно согласовать» → «Это нормальный корпоративный путь. Давайте я подготовлю короткие материалы и помогу собрать на встречу тех, без кого решение обычно не принимается».</t>
+        </is>
+      </c>
+      <c r="D34" s="25" t="inlineStr">
+        <is>
+          <t>«Сейчас не до проектов» → «Понимаю. Как раз поэтому предлагаю не проект «на всю компанию», а короткую встречу и потом пилот на один контур — без большой нагрузки на команду».</t>
+        </is>
+      </c>
+      <c r="E34" s="25" t="inlineStr">
+        <is>
+          <t>«Нужно через ИБ/закупки» → «Отлично, значит сразу заложим это в план. Скажите, какие документы нужны для ИБ и закупок — подготовим пакет к встрече или сразу после неё».</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A9:E9"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/скрипт КабС, ДОКИ, Смартвей.xlsx
+++ b/скрипт КабС, ДОКИ, Смартвей.xlsx
@@ -1755,7 +1755,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Компании от 100 млн ₽ · длинный цикл согласования · больше кабинетов · преддемо не на звонке: письмо на почту + заранее согласованная встреча и состав</t>
+          <t>Компании от 100 млн ₽ · читать можно почти дословно · на звонке не презентуем — письмо на почту и заранее согласованная встреча</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1793,7 +1793,7 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>0. ЧЕМ КОРП ОТЛИЧАЕТСЯ ОТ ОБЫЧНОЙ ПРОДАЖИ (шпаргалка менеджеру)</t>
+          <t>0. ШПАРГАЛКА МЕНЕДЖЕРУ (клиенту не читать)</t>
         </is>
       </c>
       <c r="B4" s="4" t="n"/>
@@ -1809,22 +1809,22 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>В корпе звонок — это не продажа и не презентация. Задача звонка: понять роль, нащупать интерес, согласовать состав и время встречи, отправить материалы на почту. Полную презентацию и «преддемо» на бегу с бухгалтером не делаем — иначе не соберём нужных ЛПР и потеряем сделку на длинном согласовании. Пилот обычно больше 10 кабинетов: отдел / филиал / 50–100+ сотрудников. Счёт — после встречи, демо со специалистом и внутреннего согласования у клиента.</t>
+          <t>Смотрите: в крупной компании звонок — это не продажа. Вам нужно понять, с кем говорите, коротко зацепить тему, договориться о встрече и сразу отправить материалы на почту. Презентацию «на бегу» с одним бухгалтером не делаем — потом тяжело собрать нужных людей. Пилот обычно больше, чем 10 кабинетов: отдел, филиал или 50–100+ человек. До счёта доходим после встречи, демо и их внутреннего согласования.</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>В корпе звонок — это не продажа и не презентация. Задача звонка: понять роль, нащупать интерес, согласовать состав и время встречи, отправить материалы на почту. Полную презентацию и «преддемо» на бегу с бухгалтером не делаем — иначе не соберём нужных ЛПР и потеряем сделку на длинном согласовании. Пилот обычно больше 10 кабинетов: отдел / филиал / 50–100+ сотрудников. Счёт — после встречи, демо со специалистом и внутреннего согласования у клиента.</t>
+          <t>Смотрите: в крупной компании звонок — это не продажа. Вам нужно понять, с кем говорите, коротко зацепить тему, договориться о встрече и сразу отправить материалы на почту. Презентацию «на бегу» с одним бухгалтером не делаем — потом тяжело собрать нужных людей. Пилот обычно больше, чем 10 кабинетов: отдел, филиал или 50–100+ человек. До счёта доходим после встречи, демо и их внутреннего согласования.</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>В корпе звонок — это не продажа и не презентация. Задача звонка: понять роль, нащупать интерес, согласовать состав и время встречи, отправить материалы на почту. Полную презентацию и «преддемо» на бегу с бухгалтером не делаем — иначе не соберём нужных ЛПР и потеряем сделку на длинном согласовании. Пилот обычно больше 10 кабинетов: отдел / филиал / 50–100+ сотрудников. Счёт — после встречи, демо со специалистом и внутреннего согласования у клиента.</t>
+          <t>Смотрите: в крупной компании звонок — это не продажа. Вам нужно понять, с кем говорите, коротко зацепить тему, договориться о встрече и сразу отправить материалы на почту. Презентацию «на бегу» с одним бухгалтером не делаем — потом тяжело собрать нужных людей. Пилот обычно больше, чем 10 кабинетов: отдел, филиал или 50–100+ человек. До счёта доходим после встречи, демо и их внутреннего согласования.</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>В корпе звонок — это не продажа и не презентация. Задача звонка: понять роль, нащупать интерес, согласовать состав и время встречи, отправить материалы на почту. Полную презентацию и «преддемо» на бегу с бухгалтером не делаем — иначе не соберём нужных ЛПР и потеряем сделку на длинном согласовании. Пилот обычно больше 10 кабинетов: отдел / филиал / 50–100+ сотрудников. Счёт — после встречи, демо со специалистом и внутреннего согласования у клиента.</t>
+          <t>Смотрите: в крупной компании звонок — это не продажа. Вам нужно понять, с кем говорите, коротко зацепить тему, договориться о встрече и сразу отправить материалы на почту. Презентацию «на бегу» с одним бухгалтером не делаем — потом тяжело собрать нужных людей. Пилот обычно больше, чем 10 кабинетов: отдел, филиал или 50–100+ человек. До счёта доходим после встречи, демо и их внутреннего согласования.</t>
         </is>
       </c>
     </row>
@@ -1847,22 +1847,22 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Добрый день, [ИО]! Компания «[название]», верно? Меня зовут [имя], я из «Форуса» — мы ваш партнёр по 1С. Звоню ненадолго: у нас есть сервисы по электронному документообороту с сотрудниками и контрагентами. Подскажите, пожалуйста, удобно ли сейчас буквально 3–4 минуты, чтобы понять, кому из коллег это будет полезно, и договориться о короткой встрече?</t>
+          <t>Добрый день, [ИО]! Компания «[название]», верно? Меня зовут [имя], я из «Форуса» — мы ваш партнёр по 1С. Звоню буквально на пару минут: есть сервисы, которые помогают убрать бумажную рутину с сотрудниками и с контрагентами. Подскажите, сейчас удобно совсем коротко поговорить — и если тема живая, просто договоримся о встрече?</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Добрый день, [ИО]! Компания «[название]», верно? Меня зовут [имя], я из «Форуса» — мы ваш партнёр по 1С. Звоню ненадолго: у нас есть сервисы по электронному документообороту с сотрудниками и контрагентами. Подскажите, пожалуйста, удобно ли сейчас буквально 3–4 минуты, чтобы понять, кому из коллег это будет полезно, и договориться о короткой встрече?</t>
+          <t>Добрый день, [ИО]! Компания «[название]», верно? Меня зовут [имя], я из «Форуса» — мы ваш партнёр по 1С. Звоню буквально на пару минут: есть сервисы, которые помогают убрать бумажную рутину с сотрудниками и с контрагентами. Подскажите, сейчас удобно совсем коротко поговорить — и если тема живая, просто договоримся о встрече?</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Добрый день, [ИО]! Компания «[название]», верно? Меня зовут [имя], я из «Форуса» — мы ваш партнёр по 1С. Звоню ненадолго: у нас есть сервисы по электронному документообороту с сотрудниками и контрагентами. Подскажите, пожалуйста, удобно ли сейчас буквально 3–4 минуты, чтобы понять, кому из коллег это будет полезно, и договориться о короткой встрече?</t>
+          <t>Добрый день, [ИО]! Компания «[название]», верно? Меня зовут [имя], я из «Форуса» — мы ваш партнёр по 1С. Звоню буквально на пару минут: есть сервисы, которые помогают убрать бумажную рутину с сотрудниками и с контрагентами. Подскажите, сейчас удобно совсем коротко поговорить — и если тема живая, просто договоримся о встрече?</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Добрый день, [ИО]! Компания «[название]», верно? Меня зовут [имя], я из «Форуса» — мы ваш партнёр по 1С. Звоню ненадолго: у нас есть сервисы по электронному документообороту с сотрудниками и контрагентами. Подскажите, пожалуйста, удобно ли сейчас буквально 3–4 минуты, чтобы понять, кому из коллег это будет полезно, и договориться о короткой встрече?</t>
+          <t>Добрый день, [ИО]! Компания «[название]», верно? Меня зовут [имя], я из «Форуса» — мы ваш партнёр по 1С. Звоню буквально на пару минут: есть сервисы, которые помогают убрать бумажную рутину с сотрудниками и с контрагентами. Подскажите, сейчас удобно совсем коротко поговорить — и если тема живая, просто договоримся о встрече?</t>
         </is>
       </c>
     </row>
@@ -1874,29 +1874,29 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Подскажите, вы скорее курируете решения по персоналу и процессам в целом? Сколько примерно сотрудников в компании / группе? Есть ли филиалы или удалённый персонал? Кто обычно принимает решение по таким сервисам — вы, финансовый блок, кадры, IT?</t>
+          <t>Скажите, пожалуйста, вы больше про общие решения по компании, да? А сколько у вас примерно сотрудников? Есть филиалы или удалённые? И подскажите: по таким сервисам решение обычно за вами, или ещё финансы, кадры, IT подключаются?</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Подскажите, вы главный бухгалтер / руководитель расчётного блока? Сколько roughly сотрудников на расчёте? Работаете в 1С:ЗУП / ERP? По таким темам вы сами смотрите или подключаете кадры и IT?</t>
+          <t>Подскажите, вы главный бухгалтер или руководите расчётами? Сколько примерно людей у вас на расчёте? В 1С:ЗУП работаете или в ERP? А такие темы вы сами смотрите — или обычно ещё кадры и IT зовёте?</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Подскажите, вы руководите кадровой службой / ОКП? Какой примерно штат и как сейчас устроен обмен документами с сотрудниками? Кого ещё важно подключить, если будем смотреть кадровый электронный документооборот?</t>
+          <t>Скажите, вы как раз за кадры отвечаете? Какой примерно штат, и как сейчас с документами у сотрудников — всё на бумаге или уже что-то электронное есть? Если будем смотреть КЭДО — кого ещё хорошо бы позвать?</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>Подскажите, вы отвечаете за 1С / информационную безопасность / инфраструктуру? Какой контур 1С сейчас: ЗУП, ERP, несколько баз? По новым сервисам кто ещё должен быть на встрече — кадры, бухгалтерия, ИБ?</t>
+          <t>Подскажите, вы больше про 1С и инфраструктуру, да? А сейчас у вас ЗУП, ERP, несколько баз? Если будем смотреть новый сервис — кого ещё стоит позвать: кадры, бухгалтерию, ИБ?</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2. ДОКИ — коротко на звонке, детали — на почту и встречу</t>
+          <t>2. ДОКИ — коротко на звонке, детали на почту и на встречу</t>
         </is>
       </c>
       <c r="B9" s="4" t="n"/>
@@ -1904,7 +1904,7 @@
       <c r="D9" s="4" t="n"/>
       <c r="E9" s="4" t="n"/>
     </row>
-    <row r="10" ht="85" customHeight="1">
+    <row r="10" ht="90" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Заход ДОКИ</t>
@@ -1912,22 +1912,22 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>[ИО], по ИТС ПРОФ у вас доступно бесплатное подключение «ДОКИ» на три месяца с безлимитным обменом документов. В крупных компаниях это обычно смотрят вместе с бухгалтерией и IT — не в формате «сейчас на телефоне», а на встрече. Могу коротко уточнить текущую схему и прислать описание на почту.</t>
+          <t>[ИО], смотрите: у вас есть ИТС ПРОФ, и в него входит бесплатное подключение «ДОКИ» на три месяца — с безлимитным обменом документов. В больших компаниях это обычно смотрят не по телефону, а вместе с бухгалтерией и IT. Давайте я буквально два вопроса задам — и пришлю описание на почту, хорошо?</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>[ИО], по ИТС ПРОФ у вас доступно бесплатное подключение «ДОКИ» на три месяца с безлимитным обменом документов. В крупных компаниях это обычно смотрят вместе с бухгалтерией и IT — не в формате «сейчас на телефоне», а на встрече. Могу коротко уточнить текущую схему и прислать описание на почту.</t>
+          <t>[ИО], смотрите: у вас есть ИТС ПРОФ, и в него входит бесплатное подключение «ДОКИ» на три месяца — с безлимитным обменом документов. В больших компаниях это обычно смотрят не по телефону, а вместе с бухгалтерией и IT. Давайте я буквально два вопроса задам — и пришлю описание на почту, хорошо?</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>[ИО], «ДОКИ» — это скорее про обмен с контрагентами, не про кадры. Если для бухгалтерии актуально — отмечу и пришлю материалы. Для вас важнее будет Кабинет сотрудника — его как раз и вынесем на встречу.</t>
+          <t>[ИО], смотрите, «ДОКИ» — это больше про обмен с контрагентами, не про кадры. Если бухгалтерии будет интересно — я им материалы скину. А для вас давайте лучше про Кабинет сотрудника — его как раз на встречу и вынесем.</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>[ИО], по ИТС ПРОФ у вас доступно бесплатное подключение «ДОКИ» на три месяца с безлимитным обменом документов. В крупных компаниях это обычно смотрят вместе с бухгалтерией и IT — не в формате «сейчас на телефоне», а на встрече. Могу коротко уточнить текущую схему и прислать описание на почту.</t>
+          <t>[ИО], смотрите: у вас есть ИТС ПРОФ, и в него входит бесплатное подключение «ДОКИ» на три месяца — с безлимитным обменом документов. В больших компаниях это обычно смотрят не по телефону, а вместе с бухгалтерией и IT. Давайте я буквально два вопроса задам — и пришлю описание на почту, хорошо?</t>
         </is>
       </c>
     </row>
@@ -1939,26 +1939,26 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Как сейчас обмениваетесь документами с контрагентами — несколько операторов ЭДО или единый контур? Есть ли требование, чтобы всё шло из 1С, без отдельных кабинетов?</t>
+          <t>А как вы сейчас с контрагентами документами меняетесь — через одного оператора или через несколько? И важно ли вам, чтобы всё шло прямо из 1С, без отдельных кабинетов?</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Работаете из 1С или через веб-кабинеты операторов? Насколько для вас критичен единый контур и нагрузка на бухгалтерию при больших объёмах?</t>
+          <t>Скажите, вы из 1С отправляете или через веб-кабинет оператора заходите? При больших объёмах это сильно время отъедает?</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Для кадровика: «Хорошо, ДОКИ оставим для бухгалтерии. На встрече сфокусируемся на Кабинете сотрудника».</t>
+          <t>Для кадровика: «Хорошо, тогда «ДОКИ» оставим для бухгалтерии. Давайте лучше про Кабинет сотрудника — он как раз про вашу работу».</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>Как сейчас устроена интеграция ЭДО с вашими базами 1С? Нужна ли будет оценка со стороны IT/ИБ, если подключим «ДОКИ» в контур?</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="95" customHeight="1">
+          <t>А как сейчас ЭДО с вашими базами 1С стыкуется? Если будем подключать «ДОКИ», IT или ИБ обычно тоже смотрят, да?</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="100" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Презентация ДОКИ</t>
@@ -1966,29 +1966,29 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>Коротко: «1С:ДОКИ» — ЭДО от 1С и «Калуга Астрал». Можно встроить в вашу 1С или работать через веб. По ИТС ПРОФ — три месяца безлимита, можно попробовать и не продлевать. В корпе детали и схему подключения лучше разобрать на встрече с бухгалтерией и IT. Я пришлю описание на почту — без обязательств.</t>
+          <t>Понял(а) вас. Смотрите, коротко: «1С:ДОКИ» — это ЭДО от 1С и «Калуга Астрал». Можно подвязать к вашей 1С — кнопка «Отправить» прямо в документах. А можно через веб, даже без привязки к 1С. По ИТС ПРОФ три месяца безлимита бесплатно: попробуете — если не зайдёт, можно не продлевать. Давайте детали уже на встрече разберём, с бухгалтерией и IT. Я на почту описание пришлю — ни к чему не обязывает.</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>Коротко: «1С:ДОКИ» — ЭДО от 1С и «Калуга Астрал». Можно встроить в вашу 1С или работать через веб. По ИТС ПРОФ — три месяца безлимита, можно попробовать и не продлевать. В корпе детали и схему подключения лучше разобрать на встрече с бухгалтерией и IT. Я пришлю описание на почту — без обязательств.</t>
+          <t>Понял(а) вас. Смотрите, коротко: «1С:ДОКИ» — это ЭДО от 1С и «Калуга Астрал». Можно подвязать к вашей 1С — кнопка «Отправить» прямо в документах. А можно через веб, даже без привязки к 1С. По ИТС ПРОФ три месяца безлимита бесплатно: попробуете — если не зайдёт, можно не продлевать. Давайте детали уже на встрече разберём, с бухгалтерией и IT. Я на почту описание пришлю — ни к чему не обязывает.</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Кратко: «Это для контрагентов. Материалы бухгалтеру отправлю. На встрече разберём сервис для кадров».</t>
+          <t>Кратко: «Это для контрагентов, бухгалтеру материалы отправлю. А давайте на встрече уже Кабинет сотрудника разберём — он для кадров».</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>Коротко: «1С:ДОКИ» — ЭДО от 1С и «Калуга Астрал». Можно встроить в вашу 1С или работать через веб. По ИТС ПРОФ — три месяца безлимита, можно попробовать и не продлевать. В корпе детали и схему подключения лучше разобрать на встрече с бухгалтерией и IT. Я пришлю описание на почту — без обязательств.</t>
+          <t>Понял(а) вас. Смотрите, коротко: «1С:ДОКИ» — это ЭДО от 1С и «Калуга Астрал». Можно подвязать к вашей 1С — кнопка «Отправить» прямо в документах. А можно через веб, даже без привязки к 1С. По ИТС ПРОФ три месяца безлимита бесплатно: попробуете — если не зайдёт, можно не продлевать. Давайте детали уже на встрече разберём, с бухгалтерией и IT. Я на почту описание пришлю — ни к чему не обязывает.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>3. 1С:КАБИНЕТ СОТРУДНИКА — сбор потребности на звонке (без полной презентации)</t>
+          <t>3. 1С:КАБИНЕТ СОТРУДНИКА — на звонке только вопросы, без полной презентации</t>
         </is>
       </c>
       <c r="B13" s="4" t="n"/>
@@ -1996,7 +1996,7 @@
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
     </row>
-    <row r="14" ht="125" customHeight="1">
+    <row r="14" ht="130" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Вопросы КабС</t>
@@ -2004,26 +2004,26 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Как сейчас у вас в компании устроен кадровый документооборот в масштабе — филиалы, удалёнка, согласования между подразделениями? Уже смотрели КЭДО или это пока на бумаге / в разрозненных инструментах? Если пилот — с какого контура логичнее начать: один филиал, одно юрлицо, один блок?</t>
+          <t>[ИО], а давайте вот про что: как у вас сейчас с кадровыми документами по компании? Филиалы, удалёнка, согласования между отделами — всё на бумаге или уже что-то электронное есть? КЭДО смотрели когда-нибудь? И если пробовать — с чего вам логичнее начать: один филиал, одно юрлицо, один отдел?</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Как сейчас массово выдаёте расчётные листки и фиксируете ознакомление по ст. 136? При проверках быстро находите подтверждения? Насколько расчётный блок перегружен рутиной на большом штате?</t>
+          <t>[ИО], смотрите, по статье 136 нужно извещать сотрудников о зарплате. Как вы сейчас расчётные листки раздаёте на таком штате? И если проверка — быстро найдёте, что человек ознакомился? Расчётный блок от этой рутины сильно устаёт?</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>Как сотрудники подают заявления и запрашивают справки при штате в сотни человек? Где узкое место: график отпусков, приём, удалённые сотрудники, архив? Какой отдел или филиал можно было бы взять в пилот?</t>
+          <t>[ИО], расскажите, пожалуйста: как у вас сотрудники заявления подают и справки просят, когда людей уже сотни? Где больше всего горит — отпуска, приём, удалённые, архив? А какой отдел или филиал можно было бы спокойно взять на пробу?</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>Документы кадров где хранятся и как стыкуются с 1С:ЗУП / ERP? Какие требования ИБ к облаку, локальной версии, ФСТЭК? Сколько примерно контуров/баз нужно будет учесть при внедрении?</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="120" customHeight="1">
+          <t>[ИО], а где у вас сейчас кадровые документы живут и как это с 1С связано? По безопасности какие требования — облако можно, или только локально, ФСТЭК и всё такое? Баз несколько или один контур?</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="125" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Тизер КабС
@@ -2032,57 +2032,57 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Не буду сейчас читать вам всю презентацию по телефону — в корпоративном формате это лучше сделать на встрече с нужным составом. Суть коротко: «1С:Кабинет сотрудника» — как Госуслуги для сотрудников, но внутри вашей 1С. Для крупных компаний обычно идём поэтапно: пилот на отдел или филиал, потом масштабирование. Стоимость на человека небольшая, эффект — на объёме. Детали, экономику и план внедрения пришлю на почту и разберём на встрече.</t>
+          <t>Смотрите, всю презентацию сейчас по телефону читать не буду — в вашей компании это лучше при нужных людях разобрать. Если совсем коротко: «1С:Кабинет сотрудника» — это как Госуслуги для ваших сотрудников, только рядом с вашей 1С. Обычно начинаем не со всей компании, а с отдела или филиала, смотрим как зайдёт, и потом расширяем. Стоимость на человека небольшая, а эффект как раз на большом штате чувствуется. Давайте я материалы на почту скину — и на встрече уже спокойно всё разберём.</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>На большом штате главная история — расчётные листки с ознакомлением и меньше ручного труда. Полностью сервис показывать сейчас не буду: пришлю материалы и предложу встречу, где будем с цифрами и сценариями под ваш контур.</t>
+          <t>Понял(а) вас. На большом штате чаще всего боль про расчётные листки и ручной труд. Сейчас сервис целиком рисовать не буду — это на встрече лучше ляжет. Я пришлю материалы, и давайте назначим время: там уже с цифрами и под ваш процесс посмотрим.</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Для кадров это снятие потока однотипных обращений и заявления сразу в 1С. В корпе важно не «подключить всех завтра», а выбрать пилотный контур. Давайте согласуем встречу и состав — так будет предметнее.</t>
+          <t>Смотрите, для кадров это в первую очередь меньше одних и тех же вопросов и заявления, которые сразу в 1С падают. Только давайте не будем про «подключить всех завтра» — лучше выбрать, с кого начать. Договоримся о встрече и составе — так будет гораздо полезнее.</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Для IT важны контур, безопасность и нагрузка на внедрение. Это как раз вопросы не для телефонной презентации. Пришлю описание архитектуры и предложу встречу с участием кадров/бухгалтерии.</t>
+          <t>Понял(а). Для IT как раз важны безопасность и как это ляжет на вашу 1С — по телефону это плохо разбирается. Давайте я описание пришлю, и соберём короткую встречу вместе с кадрами или бухгалтерией.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="110" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Коммерческий
-акцент КОРП</t>
+          <t>Про деньги
+и пилот</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>В корпоративном сегменте мы не предлагаем «подключить всех завтра». Обычно: пилот на филиал / юрлицо / 50–100+ кабинетов → оценка → тираж. Согласование у вас может занять время — поэтому лучше заранее заложить этапы и подключить всех, кто влияет на решение.</t>
+          <t>Смотрите, мы же не предлагаем завтра всю компанию пересадить. Обычно берём филиал, юрлицо или, скажем, 50–100 человек, пробуем, смотрим — и только потом расширяем. Согласование у вас может подольше идти, поэтому лучше сразу позвать тех, кто потом будет решение принимать.</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Ориентир по цене — от 21–30 ₽/мес за кабинет, на объёме считается отдельно. Для старта важнее согласовать пилотный контур и экономику на ваш штат — подготовлю расчёт к встрече.</t>
+          <t>По цене ориентир — от 21 до 30 рублей в месяц за человека, на объёме посчитаем отдельно. Давайте к встрече я уже прикину цифры на ваш штат — так разговор будет предметнее.</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Пилот лучше брать не «10 человек для галочки», а реальный отдел или филиал, чтобы кадры увидели эффект на потоке. Шаблоны документов перехода на КЭДО дадим.</t>
+          <t>Смотрите, пилот лучше брать не «десять человек для галочки», а нормальный отдел или филиал — чтобы вы реально увидели, стало ли легче. Шаблоны документов для перехода на КЭДО мы тоже дадим.</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>Внедрение планируем как проект: доступы, ИБ, тестовый контур, обучение ключевых пользователей. На встрече покажем схему — без сюрпризов для IT.</t>
+          <t>По внедрению тоже без сюрпризов: доступы, вопросы безопасности, обучение ключевых людей. На встрече схему покажем — вам будет понятно, сколько это от IT потребует.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>4. ГЛАВНОЕ ОТЛИЧИЕ КОРП: ПОЧТА + ВСТРЕЧА (преддемо на звонке с бухгалтером НЕ делаем)</t>
+          <t>4. ГЛАВНОЕ В КОРПЕ: ПОЧТА + ВСТРЕЧА (на звонке с бухгалтером преддемо не делаем)</t>
         </is>
       </c>
       <c r="B17" s="4" t="n"/>
@@ -2090,7 +2090,7 @@
       <c r="D17" s="4" t="n"/>
       <c r="E17" s="4" t="n"/>
     </row>
-    <row r="18" ht="130" customHeight="1">
+    <row r="18" ht="125" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Договорённость
@@ -2099,26 +2099,26 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Предлагаю не углубляться сейчас, а провести короткую рабочую встречу на 30–40 минут. На ней покажем логику сервиса и возможный пилот под ваш масштаб. Подскажите, кого важно пригласить с вашей стороны — финансы, кадры, IT, возможно ИБ или юридический блок? Какие дни на следующей неделе вам удобны?</t>
+          <t>Давайте так: сейчас глубоко не полезем, а соберём короткую встречу минут на 30–40. Там спокойно покажем, как сервис работает, и подумаем, с какого куска компании начать. Подскажите, кого с вашей стороны лучше позвать — финансы, кадры, IT, может ИБ? На следующей неделе какие дни вам удобнее?</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Полную презентацию на этом звонке проводить не буду — в вашем формате это обычно требует участия кадров и иногда IT. Давайте согласуем встречу: я пришлю материалы на почту заранее, чтобы вы могли посмотреть и позвать нужных коллег. Когда удобнее — на этой неделе или на следующей?</t>
+          <t>Смотрите, всю презентацию в этом звонке делать не буду — у вас обычно ещё кадры нужны, иногда IT. Давайте лучше встречу согласуем: я заранее на почту всё пришлю, вы посмотрите и нужных коллег позовёте. Вам удобнее на этой неделе или на следующей?</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Чтобы встреча была полезной, хорошо бы участие кадровой службы и того, кто согласовывает такие проекты. Могу провести встречу онлайн. Подскажите удобные слоты и почту, куда направить Reminder и материалы.</t>
+          <t>Чтобы встреча пользы дала, хорошо бы кадры и того, кто такие вещи согласовывает. Можем онлайн. Подскажите, какие слоты живые, и на какую почту материалы кинуть?</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Для IT как раз удобнее не телефонный разбор, а встреча с повесткой: архитектура, безопасность, этапы. Пришлю материалы заранее. Кого ещё подключить — кадры и бухгалтерию? Когда у вас есть окно на 30–40 минут?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="125" customHeight="1">
+          <t>Для IT как раз лучше не по телефону, а на встрече: как устроено, безопасность, этапы. Я материалы заранее пришлю. Кадры и бухгалтерию тоже зовём? Когда у вас минут 30–40 найдётся?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="120" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Что отправить
@@ -2127,22 +2127,22 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>После звонка обязательно письмо: краткая цель встречи, предлагаемые дата/время, рекомендуемый состав участников, презентация / одностраничник по Кабинету сотрудника, при необходимости — блок про ДОКИ и вопросник «что уточнить до встречи». Тема письма понятная: «Материалы к встрече по 1С:Кабинет сотрудника — [Компания]».</t>
+          <t>После звонка в тот же день письмо: зачем встреча, дата и время, кого желательно позвать, презентация или короткое описание Кабинета сотрудника, если надо — пару слов про ДОКИ. Тема простая: «Материалы к встрече по 1С:Кабинет сотрудника — [Компания]».</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>В письме бухгалтеру: зачем встреча, кто желателен в составе, коротко про расчётные листки и пилот, вложение с описанием сервиса, просьба подтвердить слот или предложить другой.</t>
+          <t>Бухгалтеру пишем по-человечески: зачем встреча, кого ещё хорошо бы видеть, что там про расчётные листки и пилот, вложение с описанием, и просьба подтвердить время или предложить другое.</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>В письме кадровику: фокус на заявлениях, отпусках, пилотном отделе/филиале, просьба позвать руководителя СУП / того, кто принимает решение. Без давления — «чтобы встреча прошла предметно».</t>
+          <t>Кадровику — про заявления, отпуска, с какого отдела/филиала можно начать, и просьба позвать руководителя или того, кто решение принимает. Без давления, просто: «чтобы встреча была по делу».</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>В письме IT: архитектура/контур 1С, хранение в базе клиента, ФСТЭК/локальная версия, повестка встречи, просьба подтвердить участие ИБ при необходимости.</t>
+          <t>IT — коротко: как связано с 1С, где хранятся документы, ФСТЭК/локальная версия, повестка встречи, и если нужно — позвать ИБ.</t>
         </is>
       </c>
     </row>
@@ -2150,34 +2150,34 @@
       <c r="A20" s="7" t="inlineStr">
         <is>
           <t>Состав встречи
-(регулятор)</t>
+(себе)</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Минимум: ЛПР по процессу + кадры или финансы. Идеально: руководитель / HR / главный бухгалтер или расчётный блок / IT. Если решения идут через комитет — заранее спросить, кто готовит материалы внутрь.</t>
+          <t>Минимум — тот, кто процесс курирует, плюс кадры или финансы. Хорошо, если будут руководитель, HR, главбух или расчёты, IT. Если у них всё через совещания — сразу спросите, кто внутри материалы готовит.</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Бухгалтера одного на «преддемо в звонке» недостаточно для корп-сделки. Просим его помочь собрать состав и подтвердить время — он часто проводник, но не единственный ЛПР.</t>
+          <t>Одного бухгалтера на «расскажите мне сейчас по телефону» для корпа мало. Попросите помочь собрать людей и подтвердить время — он часто проводник, но решение обычно не только за ним.</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Кадровик — ключевой пользователь. На встрече нужен тот, кто влияет на выбор пилотного контура.</t>
+          <t>Кадровик — ключевой человек. На встрече нужен ещё тот, кто скажет: «да, вот с этого отдела начнём».</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>IT нужен не всегда на первом тизере, но на корп-встрече лучше сразу, чтобы не получить стоп после «нам понравилось, но ИБ не пустит».</t>
+          <t>IT лучше сразу звать на корп-встречу. Иначе бывает: всем понравилось, а потом ИБ сказал «стоп».</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>5. СКРИПТ ВСТРЕЧИ / ПРЕДДЕМО (уже не звонок) — сбор потребности → презентация → следующий шаг</t>
+          <t>5. ВСТРЕЧА / ПРЕДДЕМО — уже не звонок: вопросы → рассказ → следующий шаг</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -2185,7 +2185,7 @@
       <c r="D21" s="4" t="n"/>
       <c r="E21" s="4" t="n"/>
     </row>
-    <row r="22" ht="95" customHeight="1">
+    <row r="22" ht="110" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Старт встречи</t>
@@ -2193,54 +2193,53 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Спасибо, что выделили время. Цель встречи на 30–40 минут: уточнить, как у вас устроены процессы, коротко показать «1С:Кабинет сотрудника» и понять, имеет ли смысл пилот на выбранном контуре. В конце зафиксируем следующий шаг — демо со специалистом или подготовка коммерческого предложения.</t>
+          <t>Спасибо большое, что выделили время. Давайте так: минут 30–40 посмотрим, как у вас сейчас процессы устроены, коротко покажу «1С:Кабинет сотрудника» и поймём, есть ли смысл пробовать на каком-то одном участке. В конце просто решим, что дальше — демо со специалистом или уже коммерческое предложение.</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Сфокусируемся на расчётных листках, нагрузке расчётного блока и том, как выглядит пилот без ломки текущих процессов.</t>
+          <t>Давайте сегодня больше про расчётные листки и нагрузку на расчёты — и как можно попробовать без ломки того, что у вас уже работает.</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Сфокусируемся на заявлениях, отпусках, самообслуживании сотрудников и пилотном контуре для кадров.</t>
+          <t>Давайте сегодня больше про заявления, отпуска и как сотрудникам проще жить — и с какого отдела вам спокойнее начать.</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Сфокусируемся на контуре 1С, безопасности, этапах внедрения и роли IT.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="115" customHeight="1">
+          <t>Давайте сегодня больше про вашу 1С, безопасность и как внедрение обычно проходит — чтобы IT было спокойно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="120" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Глубокий сбор
-потребности</t>
+          <t>Сбор потребности</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Где сейчас теряется время и управляемость: согласования, филиалы, удалёнка, проверки? Кто внутри будет спонсором проекта? Какой горизонт решения — этот квартал, полугодие? Пилот: какой филиал/юрлицо/численность реалистичны?</t>
+          <t>Скажите, а где сейчас больше всего времени и нервов уходит — согласования, филиалы, удалёнка, проверки? Кто внутри обычно такие проекты двигает? По срокам вы сейчас в каком режиме — этот квартал, ближе к полугодию? И если пробовать — какой филиал или юрлицо реально взять?</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Как закрываете ст. 136 на всём штате? Сколько времени уходит на расчётки, справки, уточнения? Что будет критерием успеха пилота для финансового блока?</t>
+          <t>А как вы сейчас по всей компании со статьёй 136 живёте? Сколько времени на расчётки, справки, уточнения уходит? И вот если пилот делать — по каким признакам вы скажете: «ок, зашло»?</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>Сколько обращений «где справка / сколько дней отпуска» в неделю? Как работаете с удалёнными и с приёмом? Какой отдел готов быть пилотным и почему?</t>
+          <t>А много ли к вам приходит вопросов вроде «где справка» и «сколько дней отпуска осталось»? С удалёнными и с приёмом как сейчас? Какой отдел готов первым попробовать — и почему именно он?</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>Какие требования к хранению данных и доступу? Сколько баз/контуров? Нужны ли анкета ИБ, тестовый контур, согласование службы безопасности?</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="115" customHeight="1">
+          <t>Подскажите по безопасности: где данные можно хранить, какие требования? Баз много? Нужна ли вам анкета для ИБ, тестовая среда, отдельное согласование?</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="125" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
           <t>Презентация
@@ -2249,57 +2248,56 @@
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>Показываем логику: сотрудник работает как в Госуслугах — заявления, документы, статусы. Для компании — прозрачные согласования и готовность к КЭДО без аврала. Акцент на масштабе: пилот → тираж, единые правила, меньше бумаги и хаоса между филиалами. Экологию упоминаем коротко. Дальше — дорожная карта и роль каждого блока.</t>
+          <t>Смотрите, логика такая: для сотрудника это как Госуслуги — заявления, документы, статусы, всё на виду. Для компании — нормальные согласования и спокойный путь к КЭДО, без аврала. В больших компаниях обычно делаем так: сначала пилот, потом расширяем на остальные. Бумаги станет меньше — это и для экологии плюс, но главное, конечно, про порядок и время. Давайте дальше по шагам пройдёмся — кто что делает.</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Акцент: расчётные листки с ознакомлением, меньше ручного труда, данные в 1С, понятная экономика на объёме. Не обещаем «внедрим за день» — показываем этапы.</t>
+          <t>Смотрите, для вас ключевое — расчётные листки с ознакомлением, меньше ручной работы и чтобы данные сразу в 1С попадали. На объёме это уже нормальные деньги и время. Мы не говорим «внедрим за день» — давайте этапы честно разберём.</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>Акцент: самообслуживание, заявления в 1С, пилотный отдел/филиал, шаблоны документов перехода, снижение потока однотипных вопросов.</t>
+          <t>Смотрите, для кадров история простая: сотрудник сам многое делает, заявления приходят в 1С, меньше одних и тех же вопросов. Берём один отдел или филиал, пробуем. Шаблоны документов для перехода мы дадим — вы не будете с нуля изобретать.</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Акцент: хранение в базе клиента, ФСТЭК/локальная версия, этапы внедрения, минимальная нагрузка на IT при поддержке Форус, стыковка с ЗУП/ERP.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="110" customHeight="1">
+          <t>Смотрите, для IT важно: документы в вашей базе, не в чужом облаке. Есть локальная версия, ФСТЭК у дата-центра 1С. Мы настройку берём на себя, стыкуемся с ЗУП или ERP. Давайте схему по этапам разберём — сколько это от вас потребует.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="115" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Закрытие встречи
-(не сразу счёт)</t>
+          <t>Закрытие встречи</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>В корпе редко закрываем счёт в тот же день — и это нормально. Фиксируем: состав пилота (численность/контур), кто готовит внутреннее согласование, нужно ли демо со специалистом, срок обратной связи. Следующий шаг: демо и/или коммерческое предложение на пилот.</t>
+          <t>Смотрите, счёт сегодня выписывать не будем — в крупных компаниях так редко бывает, и это нормально. Давайте зафиксируем: с какого участка начинаем, кто внутри дальше согласовывает, нужно ли демо со специалистом и когда вы сможете дать обратную связь. Дальше логичный шаг — демо и коммерческое предложение на пилот.</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Предлагаю следующий шаг — демонстрация со специалистом на ваших сценариях расчёток и после этого КП на пилотный контур. Вам так комфортно?</t>
+          <t>Давайте следующим шагом сделаем демонстрацию со специалистом именно на ваших расчётках — а после этого уже КП на пилот. Вам так нормально?</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Предлагаю демо на кадровых сценариях и параллельно наметить пилотный отдел. После демо подготовим КП и план обучения.</t>
+          <t>Давайте на демо разберём кадровые сценарии и параллельно наметим, с какого отдела стартуем. После демо подготовим КП и как будем обучать людей.</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Предлагаю техническое демо / ответы на вопросы ИБ и затем пилотную оценку по контурам. Какие документы от нас нужны для внутреннего согласования?</t>
+          <t>Давайте технически ещё раз всё покажем — с ответами для ИБ — и потом оценим пилот. Подскажите, какие документы вам от нас нужны, чтобы внутри согласовать?</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>6. СМАРТВЕЙ — в корпе тоже через квалификацию и передачу, без продажи «сходу»</t>
+          <t>6. СМАРТВЕЙ — тоже коротко, без продажи сходу</t>
         </is>
       </c>
       <c r="B26" s="4" t="n"/>
@@ -2315,26 +2313,26 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Есть ли регулярные командировки по филиалам / объектам? Как сейчас устроен travel: агентство, несколько сервисов, вручную? Кто владелец процесса — административный блок, финансы?</t>
+          <t>А скажите, командировки у вас регулярные — по филиалам, на объекты? Как сейчас организуете: агентство, несколько сервисов, или руками? И кто этим живёт — админы, финансы?</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Как закрываете авансовые на объёме? Данные доходят до 1С без ручного ввода? Насколько это узкое место?</t>
+          <t>А авансовые как закрываете, когда поездок много? В 1С сами попадают или всё вручную? Это сильно время ест?</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>Кто оформляет кадровые документы по командировкам при большом потоке?</t>
+          <t>А приказы и служебные по командировкам кто оформляет, когда поток большой?</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>Нужна ли интеграция travel с 1С / внутренними системами и согласование ИБ?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="95" customHeight="1">
+          <t>Скажите, travel с 1С у вас как-то связан, или всё сводите руками? ИБ на такое тоже смотрит?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="100" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
           <t>Презентация
@@ -2343,26 +2341,26 @@
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>Если командировки регулярные и их много — имеет смысл отдельный разбор. «Смартвей» как раз про единое окно и связку с 1С. В корпе это обычно отдельная встреча с профильным менеджером — я передам контакт и контекст.</t>
+          <t>Понял(а) вас. Если командировок много и они регулярные — давайте это отдельно разберём. Есть «Смартвей»: одно окно и нормальная связка с 1С. В крупных компаниях это обычно другой коллега ведёт — я передам контакт и что вы рассказали.</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>Для бухгалтерии ценность — авансовые и меньше ручного ввода в 1С. Детали и расчёт лучше даст коллега на отдельном созвоне.</t>
+          <t>Понял(а). Для бухгалтерии тут как раз про авансовые и меньше ручного ввода в 1С. Точные цифры лучше коллега на отдельном созвоне покажет — я его подключу.</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Если поток командировок большой — кадровые документы тоже страдают. Могу передать коллеге, чтобы показали стыковку с ЗУП.</t>
+          <t>Если поездок много, кадры тоже от документов устают. Могу коллеге передать — пусть покажет, как это с ЗУП стыкуется.</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>По интеграциям и безопасности коллега подготовит схему. Я передам ваш контакт и состав вопросов.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="55" customHeight="1">
+          <t>По интеграциям и безопасности коллега схему подготовит. Я ваш контакт передам и список вопросов, которые вы задали.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Передача коллеге</t>
@@ -2370,29 +2368,29 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Этим блоком занимается отдельный коллега. Я передам ваш контакт, кратко опишу масштаб и текущую схему — он предложит удобный формат встречи. Без спама и давления.</t>
+          <t>Хорошо, спасибо. Этим сервисом занимается другой мой коллега — я передам ваш контакт и коротко расскажу, как у вас сейчас устроено. Он сам напишет и предложит удобное время. Без спама, спокойно.</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Этим блоком занимается отдельный коллега. Я передам ваш контакт, кратко опишу масштаб и текущую схему — он предложит удобный формат встречи. Без спама и давления.</t>
+          <t>Хорошо, спасибо. Этим сервисом занимается другой мой коллега — я передам ваш контакт и коротко расскажу, как у вас сейчас устроено. Он сам напишет и предложит удобное время. Без спама, спокойно.</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Этим блоком занимается отдельный коллега. Я передам ваш контакт, кратко опишу масштаб и текущую схему — он предложит удобный формат встречи. Без спама и давления.</t>
+          <t>Хорошо, спасибо. Этим сервисом занимается другой мой коллега — я передам ваш контакт и коротко расскажу, как у вас сейчас устроено. Он сам напишет и предложит удобное время. Без спама, спокойно.</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Этим блоком занимается отдельный коллега. Я передам ваш контакт, кратко опишу масштаб и текущую схему — он предложит удобный формат встречи. Без спама и давления.</t>
+          <t>Хорошо, спасибо. Этим сервисом занимается другой мой коллега — я передам ваш контакт и коротко расскажу, как у вас сейчас устроено. Он сам напишет и предложит удобное время. Без спама, спокойно.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>7. ЗАВЕРШЕНИЕ ЗВОНКА (корп)</t>
+          <t>7. ЗАВЕРШЕНИЕ ЗВОНКА</t>
         </is>
       </c>
       <c r="B30" s="4" t="n"/>
@@ -2408,22 +2406,22 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Спасибо вам за время, [ИО]! Зафиксируем: я направляю материалы на почту [e-mail], встреча [дата/время], состав [роли]. Если нужно перенести или добавить участника — просто ответьте на письмо. После встречи предложим следующий шаг: демо со специалистом и проработку пилота. Хорошего дня!</t>
+          <t>Спасибо вам большое за время, [ИО]! Давайте сверём: я на почту [e-mail] отправлю материалы, встреча у нас [дата/время], с вашей стороны будут [роли]. Если нужно перенести или кого-то добавить — просто ответьте на письмо. После встречи уже решим по демо и по пилоту. Хорошего дня!</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Спасибо вам за время, [ИО]! Зафиксируем: я направляю материалы на почту [e-mail], встреча [дата/время], состав [роли]. Если нужно перенести или добавить участника — просто ответьте на письмо. После встречи предложим следующий шаг: демо со специалистом и проработку пилота. Хорошего дня!</t>
+          <t>Спасибо вам большое за время, [ИО]! Давайте сверём: я на почту [e-mail] отправлю материалы, встреча у нас [дата/время], с вашей стороны будут [роли]. Если нужно перенести или кого-то добавить — просто ответьте на письмо. После встречи уже решим по демо и по пилоту. Хорошего дня!</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>Спасибо вам за время, [ИО]! Зафиксируем: я направляю материалы на почту [e-mail], встреча [дата/время], состав [роли]. Если нужно перенести или добавить участника — просто ответьте на письмо. После встречи предложим следующий шаг: демо со специалистом и проработку пилота. Хорошего дня!</t>
+          <t>Спасибо вам большое за время, [ИО]! Давайте сверём: я на почту [e-mail] отправлю материалы, встреча у нас [дата/время], с вашей стороны будут [роли]. Если нужно перенести или кого-то добавить — просто ответьте на письмо. После встречи уже решим по демо и по пилоту. Хорошего дня!</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>Спасибо вам за время, [ИО]! Зафиксируем: я направляю материалы на почту [e-mail], встреча [дата/время], состав [роли]. Если нужно перенести или добавить участника — просто ответьте на письмо. После встречи предложим следующий шаг: демо со специалистом и проработку пилота. Хорошего дня!</t>
+          <t>Спасибо вам большое за время, [ИО]! Давайте сверём: я на почту [e-mail] отправлю материалы, встреча у нас [дата/время], с вашей стороны будут [роли]. Если нужно перенести или кого-то добавить — просто ответьте на письмо. После встречи уже решим по демо и по пилоту. Хорошего дня!</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2439,7 @@
     <row r="33" ht="48" customHeight="1">
       <c r="A33" s="14" t="inlineStr">
         <is>
-          <t>• Звонок ≠ презентация. • Письмо на почту обязательно в день звонка. • Состав встречи согласуем заранее. • Пилот считаем от реального контура (отдел/филиал/50–100+), не «10 для галочки». • Счёт — после встречи/демо и внутреннего согласования. • Ведём статус: интересант → встреча → демо → КП → согласование → пилот.</t>
+          <t>• На звонке не презентуем. • Письмо на почту — в тот же день. • Встречу и состав согласуем заранее. • Пилот — отдел/филиал/50–100+, не «10 для галочки». • Счёт — после встречи, демо и их согласования. • Цепочка: интерес → встреча → демо → КП → согласование → пилот.</t>
         </is>
       </c>
       <c r="B33" s="14" t="n"/>
@@ -2449,7 +2447,7 @@
       <c r="D33" s="14" t="n"/>
       <c r="E33" s="14" t="n"/>
     </row>
-    <row r="34" ht="110" customHeight="1">
+    <row r="34" ht="115" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
         <is>
           <t>Возражения
@@ -2458,22 +2456,22 @@
       </c>
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>«Пришлите на почту» → «Конечно, так и планировал(а). Чтобы письмо было полезным — подтвердите почту и кого ещё копировать. И давайте сразу наметим слот встречи, пока материалы свежие».</t>
+          <t>«Пришлите на почту» → «Конечно, так и хотел(а). Смотрите, чтобы письмо было по делу — подтвердите почту и кого ещё в копию поставить. И давайте сразу слот на встречу наметим, пока всё свежее».</t>
         </is>
       </c>
       <c r="C34" s="25" t="inlineStr">
         <is>
-          <t>«Мне нужно согласовать» → «Это нормальный корпоративный путь. Давайте я подготовлю короткие материалы и помогу собрать на встречу тех, без кого решение обычно не принимается».</t>
+          <t>«Мне нужно согласовать» → «Да, это нормально, у вас же большая компания. Давайте я короткие материалы подготовлю и помогу собрать на встречу тех, без кого обычно дальше не двигается».</t>
         </is>
       </c>
       <c r="D34" s="25" t="inlineStr">
         <is>
-          <t>«Сейчас не до проектов» → «Понимаю. Как раз поэтому предлагаю не проект «на всю компанию», а короткую встречу и потом пилот на один контур — без большой нагрузки на команду».</t>
+          <t>«Сейчас не до проектов» → «Понимаю вас. Поэтому я как раз не про «давайте всю компанию». Давайте короткую встречу — а дальше, если зайдёт, пилот на один участок, без большой нагрузки на людей».</t>
         </is>
       </c>
       <c r="E34" s="25" t="inlineStr">
         <is>
-          <t>«Нужно через ИБ/закупки» → «Отлично, значит сразу заложим это в план. Скажите, какие документы нужны для ИБ и закупок — подготовим пакет к встрече или сразу после неё».</t>
+          <t>«Нужно через ИБ / закупки» → «Хорошо, давайте сразу это учтём. Скажите, какие документы им нужны — подготовим к встрече или сразу после неё».</t>
         </is>
       </c>
     </row>

--- a/скрипт КабС, ДОКИ, Смартвей.xlsx
+++ b/скрипт КабС, ДОКИ, Смартвей.xlsx
@@ -1755,7 +1755,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Компании от 100 млн ₽ · читать можно почти дословно · на звонке не презентуем — письмо на почту и заранее согласованная встреча</t>
+          <t>Компании от 100 млн ₽ · тон спокойный и уважительный · на звонке не презентуем: материалы на почту и заранее согласованная встреча</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1809,22 +1809,22 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Смотрите: в крупной компании звонок — это не продажа. Вам нужно понять, с кем говорите, коротко зацепить тему, договориться о встрече и сразу отправить материалы на почту. Презентацию «на бегу» с одним бухгалтером не делаем — потом тяжело собрать нужных людей. Пилот обычно больше, чем 10 кабинетов: отдел, филиал или 50–100+ человек. До счёта доходим после встречи, демо и их внутреннего согласования.</t>
+          <t>В корпоративном сегменте первый звонок — это квалификация, а не презентация. Нужно уточнить роль собеседника, понять интерес, согласовать встречу и направить материалы на почту. Полный рассказ о продукте на звонке с одним бухгалтером не проводим: иначе сложно собрать состав для решения. Пилот обычно шире, чем 10 кабинетов — отдел, филиал или 50–100+ сотрудников. К счёту переходим после встречи, демонстрации и внутреннего согласования у клиента.</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Смотрите: в крупной компании звонок — это не продажа. Вам нужно понять, с кем говорите, коротко зацепить тему, договориться о встрече и сразу отправить материалы на почту. Презентацию «на бегу» с одним бухгалтером не делаем — потом тяжело собрать нужных людей. Пилот обычно больше, чем 10 кабинетов: отдел, филиал или 50–100+ человек. До счёта доходим после встречи, демо и их внутреннего согласования.</t>
+          <t>В корпоративном сегменте первый звонок — это квалификация, а не презентация. Нужно уточнить роль собеседника, понять интерес, согласовать встречу и направить материалы на почту. Полный рассказ о продукте на звонке с одним бухгалтером не проводим: иначе сложно собрать состав для решения. Пилот обычно шире, чем 10 кабинетов — отдел, филиал или 50–100+ сотрудников. К счёту переходим после встречи, демонстрации и внутреннего согласования у клиента.</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Смотрите: в крупной компании звонок — это не продажа. Вам нужно понять, с кем говорите, коротко зацепить тему, договориться о встрече и сразу отправить материалы на почту. Презентацию «на бегу» с одним бухгалтером не делаем — потом тяжело собрать нужных людей. Пилот обычно больше, чем 10 кабинетов: отдел, филиал или 50–100+ человек. До счёта доходим после встречи, демо и их внутреннего согласования.</t>
+          <t>В корпоративном сегменте первый звонок — это квалификация, а не презентация. Нужно уточнить роль собеседника, понять интерес, согласовать встречу и направить материалы на почту. Полный рассказ о продукте на звонке с одним бухгалтером не проводим: иначе сложно собрать состав для решения. Пилот обычно шире, чем 10 кабинетов — отдел, филиал или 50–100+ сотрудников. К счёту переходим после встречи, демонстрации и внутреннего согласования у клиента.</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>Смотрите: в крупной компании звонок — это не продажа. Вам нужно понять, с кем говорите, коротко зацепить тему, договориться о встрече и сразу отправить материалы на почту. Презентацию «на бегу» с одним бухгалтером не делаем — потом тяжело собрать нужных людей. Пилот обычно больше, чем 10 кабинетов: отдел, филиал или 50–100+ человек. До счёта доходим после встречи, демо и их внутреннего согласования.</t>
+          <t>В корпоративном сегменте первый звонок — это квалификация, а не презентация. Нужно уточнить роль собеседника, понять интерес, согласовать встречу и направить материалы на почту. Полный рассказ о продукте на звонке с одним бухгалтером не проводим: иначе сложно собрать состав для решения. Пилот обычно шире, чем 10 кабинетов — отдел, филиал или 50–100+ сотрудников. К счёту переходим после встречи, демонстрации и внутреннего согласования у клиента.</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="n"/>
     </row>
-    <row r="7" ht="78" customHeight="1">
+    <row r="7" ht="85" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Приветствие</t>
@@ -1847,26 +1847,26 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Добрый день, [ИО]! Компания «[название]», верно? Меня зовут [имя], я из «Форуса» — мы ваш партнёр по 1С. Звоню буквально на пару минут: есть сервисы, которые помогают убрать бумажную рутину с сотрудниками и с контрагентами. Подскажите, сейчас удобно совсем коротко поговорить — и если тема живая, просто договоримся о встрече?</t>
+          <t>Добрый день, [ИО]! Компания «[название]», верно? Меня зовут [имя], я из «Форуса» — мы ваш партнёр по 1С. Звоню кратко: хотел(а) предложить обсудить сервисы, которые помогают сократить бумажный документооборот с сотрудниками и контрагентами. Подскажите, пожалуйста, удобно ли вам сейчас уделить три–четыре минуты, чтобы понять, актуально ли это для вашей компании, и при необходимости согласовать встречу?</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Добрый день, [ИО]! Компания «[название]», верно? Меня зовут [имя], я из «Форуса» — мы ваш партнёр по 1С. Звоню буквально на пару минут: есть сервисы, которые помогают убрать бумажную рутину с сотрудниками и с контрагентами. Подскажите, сейчас удобно совсем коротко поговорить — и если тема живая, просто договоримся о встрече?</t>
+          <t>Добрый день, [ИО]! Компания «[название]», верно? Меня зовут [имя], я из «Форуса» — мы ваш партнёр по 1С. Звоню кратко: хотел(а) предложить обсудить сервисы, которые помогают сократить бумажный документооборот с сотрудниками и контрагентами. Подскажите, пожалуйста, удобно ли вам сейчас уделить три–четыре минуты, чтобы понять, актуально ли это для вашей компании, и при необходимости согласовать встречу?</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Добрый день, [ИО]! Компания «[название]», верно? Меня зовут [имя], я из «Форуса» — мы ваш партнёр по 1С. Звоню буквально на пару минут: есть сервисы, которые помогают убрать бумажную рутину с сотрудниками и с контрагентами. Подскажите, сейчас удобно совсем коротко поговорить — и если тема живая, просто договоримся о встрече?</t>
+          <t>Добрый день, [ИО]! Компания «[название]», верно? Меня зовут [имя], я из «Форуса» — мы ваш партнёр по 1С. Звоню кратко: хотел(а) предложить обсудить сервисы, которые помогают сократить бумажный документооборот с сотрудниками и контрагентами. Подскажите, пожалуйста, удобно ли вам сейчас уделить три–четыре минуты, чтобы понять, актуально ли это для вашей компании, и при необходимости согласовать встречу?</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Добрый день, [ИО]! Компания «[название]», верно? Меня зовут [имя], я из «Форуса» — мы ваш партнёр по 1С. Звоню буквально на пару минут: есть сервисы, которые помогают убрать бумажную рутину с сотрудниками и с контрагентами. Подскажите, сейчас удобно совсем коротко поговорить — и если тема живая, просто договоримся о встрече?</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="110" customHeight="1">
+          <t>Добрый день, [ИО]! Компания «[название]», верно? Меня зовут [имя], я из «Форуса» — мы ваш партнёр по 1С. Звоню кратко: хотел(а) предложить обсудить сервисы, которые помогают сократить бумажный документооборот с сотрудниками и контрагентами. Подскажите, пожалуйста, удобно ли вам сейчас уделить три–четыре минуты, чтобы понять, актуально ли это для вашей компании, и при необходимости согласовать встречу?</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="115" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Квалификация</t>
@@ -1874,29 +1874,29 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Скажите, пожалуйста, вы больше про общие решения по компании, да? А сколько у вас примерно сотрудников? Есть филиалы или удалённые? И подскажите: по таким сервисам решение обычно за вами, или ещё финансы, кадры, IT подключаются?</t>
+          <t>Подскажите, пожалуйста, вы курируете вопросы управления и внутренних процессов в компании? Сколько примерно сотрудников в организации? Есть ли филиалы или удалённый персонал? И кто обычно участвует в выборе таких сервисов — вы, финансовый блок, кадры, IT?</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Подскажите, вы главный бухгалтер или руководите расчётами? Сколько примерно людей у вас на расчёте? В 1С:ЗУП работаете или в ERP? А такие темы вы сами смотрите — или обычно ещё кадры и IT зовёте?</t>
+          <t>Подскажите, вы главный бухгалтер или руководитель расчётного направления? Сколько примерно сотрудников находится у вас на расчёте? Работаете в 1С:ЗУП или ERP? По таким сервисам решение принимаете самостоятельно или обычно подключаете кадры и IT?</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Скажите, вы как раз за кадры отвечаете? Какой примерно штат, и как сейчас с документами у сотрудников — всё на бумаге или уже что-то электронное есть? Если будем смотреть КЭДО — кого ещё хорошо бы позвать?</t>
+          <t>Подскажите, вы руководите кадровой службой? Какой примерно штат, и как сейчас организован обмен кадровыми документами с сотрудниками? Если будем рассматривать кадровый электронный документооборот, кого ещё целесообразно пригласить?</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>Подскажите, вы больше про 1С и инфраструктуру, да? А сейчас у вас ЗУП, ERP, несколько баз? Если будем смотреть новый сервис — кого ещё стоит позвать: кадры, бухгалтерию, ИБ?</t>
+          <t>Подскажите, вы отвечаете за 1С и инфраструктуру? Какие системы сейчас используются — ЗУП, ERP, несколько баз? Если будем обсуждать новый сервис, кого ещё стоит пригласить: кадры, бухгалтерию, службу ИБ?</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2. ДОКИ — коротко на звонке, детали на почту и на встречу</t>
+          <t>2. ДОКИ — кратко на звонке, подробности на почту и на встречу</t>
         </is>
       </c>
       <c r="B9" s="4" t="n"/>
@@ -1912,22 +1912,22 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>[ИО], смотрите: у вас есть ИТС ПРОФ, и в него входит бесплатное подключение «ДОКИ» на три месяца — с безлимитным обменом документов. В больших компаниях это обычно смотрят не по телефону, а вместе с бухгалтерией и IT. Давайте я буквально два вопроса задам — и пришлю описание на почту, хорошо?</t>
+          <t>[ИО], у вас подключён ИТС ПРОФ, и в него входит бесплатное подключение сервиса «ДОКИ» на три месяца с безлимитным обменом документов. В крупных компаниях этот вопрос обычно рассматривают совместно с бухгалтерией и IT, а не в рамках короткого телефонного разговора. Позвольте уточнить два момента — и я направлю описание на почту.</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>[ИО], смотрите: у вас есть ИТС ПРОФ, и в него входит бесплатное подключение «ДОКИ» на три месяца — с безлимитным обменом документов. В больших компаниях это обычно смотрят не по телефону, а вместе с бухгалтерией и IT. Давайте я буквально два вопроса задам — и пришлю описание на почту, хорошо?</t>
+          <t>[ИО], у вас подключён ИТС ПРОФ, и в него входит бесплатное подключение сервиса «ДОКИ» на три месяца с безлимитным обменом документов. В крупных компаниях этот вопрос обычно рассматривают совместно с бухгалтерией и IT, а не в рамках короткого телефонного разговора. Позвольте уточнить два момента — и я направлю описание на почту.</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>[ИО], смотрите, «ДОКИ» — это больше про обмен с контрагентами, не про кадры. Если бухгалтерии будет интересно — я им материалы скину. А для вас давайте лучше про Кабинет сотрудника — его как раз на встречу и вынесем.</t>
+          <t>[ИО], сервис «ДОКИ» относится к обмену документами с контрагентами, а не к кадровой работе. Если тема будет интересна бухгалтерии — направлю им материалы. Для вас предлагаю обсудить «1С:Кабинет сотрудника» — его как раз вынесем на встречу.</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>[ИО], смотрите: у вас есть ИТС ПРОФ, и в него входит бесплатное подключение «ДОКИ» на три месяца — с безлимитным обменом документов. В больших компаниях это обычно смотрят не по телефону, а вместе с бухгалтерией и IT. Давайте я буквально два вопроса задам — и пришлю описание на почту, хорошо?</t>
+          <t>[ИО], у вас подключён ИТС ПРОФ, и в него входит бесплатное подключение сервиса «ДОКИ» на три месяца с безлимитным обменом документов. В крупных компаниях этот вопрос обычно рассматривают совместно с бухгалтерией и IT, а не в рамках короткого телефонного разговора. Позвольте уточнить два момента — и я направлю описание на почту.</t>
         </is>
       </c>
     </row>
@@ -1939,26 +1939,26 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>А как вы сейчас с контрагентами документами меняетесь — через одного оператора или через несколько? И важно ли вам, чтобы всё шло прямо из 1С, без отдельных кабинетов?</t>
+          <t>Подскажите, как сейчас организован обмен документами с контрагентами — через одного оператора ЭДО или через несколько? Важно ли, чтобы отправка шла непосредственно из 1С, без отдельных веб-кабинетов?</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Скажите, вы из 1С отправляете или через веб-кабинет оператора заходите? При больших объёмах это сильно время отъедает?</t>
+          <t>Вы работаете с ЭДО из 1С или через веб-кабинет оператора? При больших объёмах документов это заметно увеличивает нагрузку на бухгалтерию?</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Для кадровика: «Хорошо, тогда «ДОКИ» оставим для бухгалтерии. Давайте лучше про Кабинет сотрудника — он как раз про вашу работу».</t>
+          <t>Для кадровика: «Хорошо, тогда «ДОКИ» оставим для бухгалтерии. Давайте перейдём к Кабинету сотрудника — он относится непосредственно к вашей работе».</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>А как сейчас ЭДО с вашими базами 1С стыкуется? Если будем подключать «ДОКИ», IT или ИБ обычно тоже смотрят, да?</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="100" customHeight="1">
+          <t>Как сейчас ЭДО связан с вашими базами 1С? Если будем рассматривать подключение «ДОКИ», потребуется ли участие IT или службы ИБ?</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="105" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Презентация ДОКИ</t>
@@ -1966,29 +1966,29 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>Понял(а) вас. Смотрите, коротко: «1С:ДОКИ» — это ЭДО от 1С и «Калуга Астрал». Можно подвязать к вашей 1С — кнопка «Отправить» прямо в документах. А можно через веб, даже без привязки к 1С. По ИТС ПРОФ три месяца безлимита бесплатно: попробуете — если не зайдёт, можно не продлевать. Давайте детали уже на встрече разберём, с бухгалтерией и IT. Я на почту описание пришлю — ни к чему не обязывает.</t>
+          <t>Благодарю вас. Сервис «1С:ДОКИ» — это электронный документооборот от 1С и «Калуга Астрал». Его можно подключить к вашей 1С: в документах появится кнопка «Отправить». Также доступна работа через веб-версию, без обязательной привязки к 1С. По ИТС ПРОФ предусмотрены три месяца безлимитного обмена бесплатно; если сервис не подойдёт, продлевать его не обязательно. Подробности удобнее разобрать на встрече с участием бухгалтерии и IT. Я направлю описание на почту — это ни к чему не обязывает.</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>Понял(а) вас. Смотрите, коротко: «1С:ДОКИ» — это ЭДО от 1С и «Калуга Астрал». Можно подвязать к вашей 1С — кнопка «Отправить» прямо в документах. А можно через веб, даже без привязки к 1С. По ИТС ПРОФ три месяца безлимита бесплатно: попробуете — если не зайдёт, можно не продлевать. Давайте детали уже на встрече разберём, с бухгалтерией и IT. Я на почту описание пришлю — ни к чему не обязывает.</t>
+          <t>Благодарю вас. Сервис «1С:ДОКИ» — это электронный документооборот от 1С и «Калуга Астрал». Его можно подключить к вашей 1С: в документах появится кнопка «Отправить». Также доступна работа через веб-версию, без обязательной привязки к 1С. По ИТС ПРОФ предусмотрены три месяца безлимитного обмена бесплатно; если сервис не подойдёт, продлевать его не обязательно. Подробности удобнее разобрать на встрече с участием бухгалтерии и IT. Я направлю описание на почту — это ни к чему не обязывает.</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Кратко: «Это для контрагентов, бухгалтеру материалы отправлю. А давайте на встрече уже Кабинет сотрудника разберём — он для кадров».</t>
+          <t>Кратко: «Это сервис для обмена с контрагентами; материалы для бухгалтерии я направлю. На встрече предлагаю разобрать Кабинет сотрудника — он для кадровой работы».</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>Понял(а) вас. Смотрите, коротко: «1С:ДОКИ» — это ЭДО от 1С и «Калуга Астрал». Можно подвязать к вашей 1С — кнопка «Отправить» прямо в документах. А можно через веб, даже без привязки к 1С. По ИТС ПРОФ три месяца безлимита бесплатно: попробуете — если не зайдёт, можно не продлевать. Давайте детали уже на встрече разберём, с бухгалтерией и IT. Я на почту описание пришлю — ни к чему не обязывает.</t>
+          <t>Благодарю вас. Сервис «1С:ДОКИ» — это электронный документооборот от 1С и «Калуга Астрал». Его можно подключить к вашей 1С: в документах появится кнопка «Отправить». Также доступна работа через веб-версию, без обязательной привязки к 1С. По ИТС ПРОФ предусмотрены три месяца безлимитного обмена бесплатно; если сервис не подойдёт, продлевать его не обязательно. Подробности удобнее разобрать на встрече с участием бухгалтерии и IT. Я направлю описание на почту — это ни к чему не обязывает.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>3. 1С:КАБИНЕТ СОТРУДНИКА — на звонке только вопросы, без полной презентации</t>
+          <t>3. 1С:КАБИНЕТ СОТРУДНИКА — на звонке уточняем потребность, полную презентацию не проводим</t>
         </is>
       </c>
       <c r="B13" s="4" t="n"/>
@@ -2004,85 +2004,84 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>[ИО], а давайте вот про что: как у вас сейчас с кадровыми документами по компании? Филиалы, удалёнка, согласования между отделами — всё на бумаге или уже что-то электронное есть? КЭДО смотрели когда-нибудь? И если пробовать — с чего вам логичнее начать: один филиал, одно юрлицо, один отдел?</t>
+          <t>[ИО], подскажите, как сейчас организован кадровый документооборот в компании: заявления, приказы, согласования между подразделениями и филиалами? Используете бумажный процесс или уже есть электронные инструменты? Если рассматривать пилот — с какого участка логичнее начать: филиал, юридическое лицо или отдел?</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>[ИО], смотрите, по статье 136 нужно извещать сотрудников о зарплате. Как вы сейчас расчётные листки раздаёте на таком штате? И если проверка — быстро найдёте, что человек ознакомился? Расчётный блок от этой рутины сильно устаёт?</t>
+          <t>[ИО], по статье 136 Трудового кодекса необходимо извещать сотрудников о составных частях зарплаты. Как сейчас организована выдача расчётных листков на вашем штате? Есть ли подтверждение ознакомления, и можно ли при необходимости быстро его найти? Насколько эта работа загружает расчётный блок?</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>[ИО], расскажите, пожалуйста: как у вас сотрудники заявления подают и справки просят, когда людей уже сотни? Где больше всего горит — отпуска, приём, удалённые, архив? А какой отдел или филиал можно было бы спокойно взять на пробу?</t>
+          <t>[ИО], расскажите, пожалуйста, как сотрудники подают заявления и запрашивают справки при значительной численности персонала? Где сейчас основная нагрузка — отпуска, приём, работа с удалёнными сотрудниками, архив? Какой отдел или филиал можно было бы рассмотреть для пилотного запуска?</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>[ИО], а где у вас сейчас кадровые документы живут и как это с 1С связано? По безопасности какие требования — облако можно, или только локально, ФСТЭК и всё такое? Баз несколько или один контур?</t>
+          <t>[ИО], где сейчас хранятся кадровые документы и насколько они связаны с вашей 1С? Какие требования к информационной безопасности предъявляются к таким сервисам — допустимо облако, нужна локальная версия, аттестация ФСТЭК? Сколько баз или контуров потребуется учесть?</t>
         </is>
       </c>
     </row>
     <row r="15" ht="125" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>Тизер КабС
-(не презентация)</t>
+          <t>Краткий обзор
+КабС</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Смотрите, всю презентацию сейчас по телефону читать не буду — в вашей компании это лучше при нужных людях разобрать. Если совсем коротко: «1С:Кабинет сотрудника» — это как Госуслуги для ваших сотрудников, только рядом с вашей 1С. Обычно начинаем не со всей компании, а с отдела или филиала, смотрим как зайдёт, и потом расширяем. Стоимость на человека небольшая, а эффект как раз на большом штате чувствуется. Давайте я материалы на почту скину — и на встрече уже спокойно всё разберём.</t>
+          <t>Полную презентацию в телефонном разговоре проводить не буду — в корпоративном формате это корректнее сделать на встрече с нужным составом участников. Если кратко: «1С:Кабинет сотрудника» — сервис самообслуживания сотрудников в контуре 1С, по логике близкий к привычным государственным сервисам: заявления, документы, статусы. Для крупных компаний обычно рекомендуем поэтапный запуск: пилот на отдел или филиал, затем расширение. Стоимость на одного сотрудника невелика, эффект проявляется на объёме. Я направлю материалы на почту, а детали и расчёт разберём на встрече.</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Понял(а) вас. На большом штате чаще всего боль про расчётные листки и ручной труд. Сейчас сервис целиком рисовать не буду — это на встрече лучше ляжет. Я пришлю материалы, и давайте назначим время: там уже с цифрами и под ваш процесс посмотрим.</t>
+          <t>Благодарю вас. При большом штате чаще всего важны расчётные листки с подтверждением ознакомления и снижение ручного труда. Сейчас не буду подробно описывать весь функционал — направлю материалы и предлагаю согласовать встречу, где разберём сценарии применительно к вашему процессу.</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Смотрите, для кадров это в первую очередь меньше одних и тех же вопросов и заявления, которые сразу в 1С падают. Только давайте не будем про «подключить всех завтра» — лучше выбрать, с кого начать. Договоримся о встрече и составе — так будет гораздо полезнее.</t>
+          <t>Для кадровой службы сервис прежде всего снижает поток однотипных обращений и позволяет получать заявления сразу в 1С. В корпоративном формате важно не подключать сразу всю компанию, а определить пилотный участок. Давайте согласуем встречу и состав участников — так обсуждение будет предметным.</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Понял(а). Для IT как раз важны безопасность и как это ляжет на вашу 1С — по телефону это плохо разбирается. Давайте я описание пришлю, и соберём короткую встречу вместе с кадрами или бухгалтерией.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="110" customHeight="1">
+          <t>Для IT обычно важны связь с 1С, модель безопасности и объём работ по внедрению — это неудобно разбирать по телефону. Я направлю описание и предлагаю короткую встречу с участием кадров или бухгалтерии.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="105" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Про деньги
-и пилот</t>
+          <t>Пилот и стоимость</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Смотрите, мы же не предлагаем завтра всю компанию пересадить. Обычно берём филиал, юрлицо или, скажем, 50–100 человек, пробуем, смотрим — и только потом расширяем. Согласование у вас может подольше идти, поэтому лучше сразу позвать тех, кто потом будет решение принимать.</t>
+          <t>Мы не предлагаем единовременно переводить на сервис всю компанию. Как правило, начинают с филиала, юридического лица или группы в 50–100 сотрудников, оценивают результат и затем расширяют. Поскольку согласование может занять время, на встречу лучше пригласить тех, кто влияет на решение.</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>По цене ориентир — от 21 до 30 рублей в месяц за человека, на объёме посчитаем отдельно. Давайте к встрече я уже прикину цифры на ваш штат — так разговор будет предметнее.</t>
+          <t>Ориентир по стоимости — от 21 до 30 рублей в месяц за сотрудника; на вашем объёме подготовим отдельный расчёт к встрече.</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Смотрите, пилот лучше брать не «десять человек для галочки», а нормальный отдел или филиал — чтобы вы реально увидели, стало ли легче. Шаблоны документов для перехода на КЭДО мы тоже дадим.</t>
+          <t>Для пилота целесообразнее взять полноценный отдел или филиал, чтобы кадровая служба увидела эффект на реальном потоке документов. Шаблоны документов для перехода на КЭДО мы подготовим.</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>По внедрению тоже без сюрпризов: доступы, вопросы безопасности, обучение ключевых людей. На встрече схему покажем — вам будет понятно, сколько это от IT потребует.</t>
+          <t>Внедрение выстраиваем поэтапно: доступы, вопросы безопасности, обучение ключевых пользователей. На встрече покажем схему работ, чтобы IT заранее понимал объём участия.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>4. ГЛАВНОЕ В КОРПЕ: ПОЧТА + ВСТРЕЧА (на звонке с бухгалтером преддемо не делаем)</t>
+          <t>4. КЛЮЧЕВОЕ ОТЛИЧИЕ КОРП: МАТЕРИАЛЫ НА ПОЧТУ И СОГЛАСОВАННАЯ ВСТРЕЧА</t>
         </is>
       </c>
       <c r="B17" s="4" t="n"/>
@@ -2099,50 +2098,50 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Давайте так: сейчас глубоко не полезем, а соберём короткую встречу минут на 30–40. Там спокойно покажем, как сервис работает, и подумаем, с какого куска компании начать. Подскажите, кого с вашей стороны лучше позвать — финансы, кадры, IT, может ИБ? На следующей неделе какие дни вам удобнее?</t>
+          <t>Предлагаю не углубляться в детали в этом разговоре, а согласовать короткую встречу на 30–40 минут. На ней покажем логику сервиса и обсудим возможный пилот. Подскажите, кого целесообразно пригласить с вашей стороны — финансы, кадры, IT, при необходимости службу ИБ? Какие дни на следующей неделе вам удобны?</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Смотрите, всю презентацию в этом звонке делать не буду — у вас обычно ещё кадры нужны, иногда IT. Давайте лучше встречу согласуем: я заранее на почту всё пришлю, вы посмотрите и нужных коллег позовёте. Вам удобнее на этой неделе или на следующей?</t>
+          <t>Полную презентацию в этом звонке проводить не буду: в вашем формате обычно требуется участие кадровой службы, иногда IT. Давайте согласуем встречу: я заранее направлю материалы на почту, чтобы вы могли ознакомиться и пригласить коллег. Вам удобнее на этой неделе или на следующей?</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Чтобы встреча пользы дала, хорошо бы кадры и того, кто такие вещи согласовывает. Можем онлайн. Подскажите, какие слоты живые, и на какую почту материалы кинуть?</t>
+          <t>Чтобы встреча была полезной, желательно участие кадровой службы и сотрудника, который согласовывает подобные проекты. Можем провести встречу онлайн. Подскажите удобное время и адрес почты для материалов.</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Для IT как раз лучше не по телефону, а на встрече: как устроено, безопасность, этапы. Я материалы заранее пришлю. Кадры и бухгалтерию тоже зовём? Когда у вас минут 30–40 найдётся?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="120" customHeight="1">
+          <t>Для IT удобнее обсуждать архитектуру и безопасность не по телефону, а на встрече с повесткой. Я заранее направлю материалы. Стоит ли сразу пригласить кадры и бухгалтерию? Когда у вас будет 30–40 минут?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="115" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>Что отправить
+          <t>Что направить
 на почту</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>После звонка в тот же день письмо: зачем встреча, дата и время, кого желательно позвать, презентация или короткое описание Кабинета сотрудника, если надо — пару слов про ДОКИ. Тема простая: «Материалы к встрече по 1С:Кабинет сотрудника — [Компания]».</t>
+          <t>В день звонка направляем письмо: цель встречи, дата и время, рекомендуемый состав участников, описание или презентацию по Кабинету сотрудника, при необходимости — краткий блок по ДОКИ. Тема письма: «Материалы к встрече по 1С:Кабинет сотрудника — [Компания]».</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Бухгалтеру пишем по-человечески: зачем встреча, кого ещё хорошо бы видеть, что там про расчётные листки и пилот, вложение с описанием, и просьба подтвердить время или предложить другое.</t>
+          <t>Бухгалтеру — зачем встреча, кого желательно пригласить, кратко о расчётных листках и пилоте, вложение с описанием сервиса, просьба подтвердить время или предложить другое.</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>Кадровику — про заявления, отпуска, с какого отдела/филиала можно начать, и просьба позвать руководителя или того, кто решение принимает. Без давления, просто: «чтобы встреча была по делу».</t>
+          <t>Кадровику — акцент на заявлениях, отпусках и выборе пилотного отдела или филиала; просьба пригласить руководителя службы или сотрудника, принимающего решение.</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>IT — коротко: как связано с 1С, где хранятся документы, ФСТЭК/локальная версия, повестка встречи, и если нужно — позвать ИБ.</t>
+          <t>IT — связь с 1С, хранение документов в базе клиента, ФСТЭК или локальная версия, повестка встречи; при необходимости — просьба привлечь службу ИБ.</t>
         </is>
       </c>
     </row>
@@ -2155,29 +2154,29 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Минимум — тот, кто процесс курирует, плюс кадры или финансы. Хорошо, если будут руководитель, HR, главбух или расчёты, IT. Если у них всё через совещания — сразу спросите, кто внутри материалы готовит.</t>
+          <t>Минимум: сотрудник, курирующий процесс, плюс кадры или финансы. Оптимально: руководитель, HR, главный бухгалтер или расчётный блок, IT. Если решения принимаются коллегиально — заранее уточните, кто готовит материалы внутри.</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Одного бухгалтера на «расскажите мне сейчас по телефону» для корпа мало. Попросите помочь собрать людей и подтвердить время — он часто проводник, но решение обычно не только за ним.</t>
+          <t>Одного бухгалтера для корпоративной сделки недостаточно. Попросите помочь согласовать состав и время: бухгалтер часто является проводником, но решение обычно принимается шире.</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Кадровик — ключевой человек. На встрече нужен ещё тот, кто скажет: «да, вот с этого отдела начнём».</t>
+          <t>Кадровик — ключевой участник. На встрече также нужен сотрудник, который определит пилотный участок.</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>IT лучше сразу звать на корп-встречу. Иначе бывает: всем понравилось, а потом ИБ сказал «стоп».</t>
+          <t>IT лучше приглашать сразу. Иначе после положительной оценки сервиса обсуждение может остановиться на этапе ИБ.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>5. ВСТРЕЧА / ПРЕДДЕМО — уже не звонок: вопросы → рассказ → следующий шаг</t>
+          <t>5. ВСТРЕЧА / ПРЕДДЕМО — уточнение потребности → презентация → следующий шаг</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -2193,22 +2192,22 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Спасибо большое, что выделили время. Давайте так: минут 30–40 посмотрим, как у вас сейчас процессы устроены, коротко покажу «1С:Кабинет сотрудника» и поймём, есть ли смысл пробовать на каком-то одном участке. В конце просто решим, что дальше — демо со специалистом или уже коммерческое предложение.</t>
+          <t>Благодарю вас за время. Предлагаю уделить 30–40 минут на то, чтобы уточнить текущие процессы, кратко показать «1С:Кабинет сотрудника» и понять, целесообразен ли пилот на выбранном участке. В завершение зафиксируем следующий шаг — демонстрацию со специалистом или подготовку коммерческого предложения.</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Давайте сегодня больше про расчётные листки и нагрузку на расчёты — и как можно попробовать без ломки того, что у вас уже работает.</t>
+          <t>Сегодня предлагаю сосредоточиться на расчётных листках, нагрузке расчётного блока и формате пилота без изменения работающих процессов.</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Давайте сегодня больше про заявления, отпуска и как сотрудникам проще жить — и с какого отдела вам спокойнее начать.</t>
+          <t>Сегодня предлагаю сосредоточиться на заявлениях, отпусках и выборе пилотного отдела для кадровой службы.</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Давайте сегодня больше про вашу 1С, безопасность и как внедрение обычно проходит — чтобы IT было спокойно.</t>
+          <t>Сегодня предлагаю сосредоточиться на связи с 1С, требованиях безопасности и этапах внедрения — чтобы IT понимал объём участия.</t>
         </is>
       </c>
     </row>
@@ -2220,26 +2219,26 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Скажите, а где сейчас больше всего времени и нервов уходит — согласования, филиалы, удалёнка, проверки? Кто внутри обычно такие проекты двигает? По срокам вы сейчас в каком режиме — этот квартал, ближе к полугодию? И если пробовать — какой филиал или юрлицо реально взять?</t>
+          <t>Подскажите, где сейчас теряется больше всего времени: согласования, филиалы, удалённые сотрудники, подготовка к проверкам? Кто внутри компании обычно курирует подобные проекты? В каком горизонте вы рассматриваете решение — в этом квартале или ближе к полугодию? Если пилот — какой филиал или юридическое лицо реалистично взять первым?</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>А как вы сейчас по всей компании со статьёй 136 живёте? Сколько времени на расчётки, справки, уточнения уходит? И вот если пилот делать — по каким признакам вы скажете: «ок, зашло»?</t>
+          <t>Как сейчас выполняется требование статьи 136 по всему штату? Сколько времени уходит на расчётные листки, справки и уточнения? По каким критериям вы оцените, что пилот прошёл успешно?</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>А много ли к вам приходит вопросов вроде «где справка» и «сколько дней отпуска осталось»? С удалёнными и с приёмом как сейчас? Какой отдел готов первым попробовать — и почему именно он?</t>
+          <t>Как часто сотрудники обращаются за справками и остатками отпуска? Как организована работа с удалёнными сотрудниками и приёмом? Какой отдел готов участвовать в пилоте и почему именно он?</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>Подскажите по безопасности: где данные можно хранить, какие требования? Баз много? Нужна ли вам анкета для ИБ, тестовая среда, отдельное согласование?</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="125" customHeight="1">
+          <t>Какие требования к хранению данных и доступу предъявляются? Сколько баз потребуется учесть? Нужны ли анкета для ИБ, тестовая среда или отдельное согласование службы безопасности?</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="130" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
           <t>Презентация
@@ -2248,22 +2247,22 @@
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>Смотрите, логика такая: для сотрудника это как Госуслуги — заявления, документы, статусы, всё на виду. Для компании — нормальные согласования и спокойный путь к КЭДО, без аврала. В больших компаниях обычно делаем так: сначала пилот, потом расширяем на остальные. Бумаги станет меньше — это и для экологии плюс, но главное, конечно, про порядок и время. Давайте дальше по шагам пройдёмся — кто что делает.</t>
+          <t>Логика сервиса такая: сотрудник работает в личном кабинете — подаёт заявления, получает документы, видит статусы. Для компании это прозрачные согласования и спокойный переход к КЭДО. В крупных организациях обычно начинаем с пилота и затем расширяем на другие подразделения. Бумажный документооборот сокращается; дополнительно снижается и экологическая нагрузка, хотя основной эффект — в порядке процессов и экономии времени. Далее предлагаю пройти этапы внедрения и роли участников.</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Смотрите, для вас ключевое — расчётные листки с ознакомлением, меньше ручной работы и чтобы данные сразу в 1С попадали. На объёме это уже нормальные деньги и время. Мы не говорим «внедрим за день» — давайте этапы честно разберём.</t>
+          <t>Для финансового блока ключевые темы — расчётные листки с подтверждением ознакомления, меньше ручного труда и попадание данных сразу в 1С. На большом штате это даёт понятный экономический эффект. Мы не обещаем внедрение за один день — этапы работ разберём отдельно.</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>Смотрите, для кадров история простая: сотрудник сам многое делает, заявления приходят в 1С, меньше одних и тех же вопросов. Берём один отдел или филиал, пробуем. Шаблоны документов для перехода мы дадим — вы не будете с нуля изобретать.</t>
+          <t>Для кадровой службы сервис снижает поток однотипных обращений: сотрудник самостоятельно решает часть вопросов, заявления поступают в 1С. Берём один отдел или филиал и оцениваем результат. Шаблоны документов для перехода на КЭДО подготовим.</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Смотрите, для IT важно: документы в вашей базе, не в чужом облаке. Есть локальная версия, ФСТЭК у дата-центра 1С. Мы настройку берём на себя, стыкуемся с ЗУП или ERP. Давайте схему по этапам разберём — сколько это от вас потребует.</t>
+          <t>Для IT важно, что документы хранятся в вашей базе 1С, а не во внешнем облаке. Доступны локальная версия и дата-центр 1С с аттестатами ФСТЭК. Настройку берём на себя, сервис стыкуется с ЗУП или ERP. Давайте разберём схему по этапам и объём участия вашей команды.</t>
         </is>
       </c>
     </row>
@@ -2275,29 +2274,29 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Смотрите, счёт сегодня выписывать не будем — в крупных компаниях так редко бывает, и это нормально. Давайте зафиксируем: с какого участка начинаем, кто внутри дальше согласовывает, нужно ли демо со специалистом и когда вы сможете дать обратную связь. Дальше логичный шаг — демо и коммерческое предложение на пилот.</t>
+          <t>Счёт по итогам этой встречи выставлять не будем — в корпоративном формате это обычно следующий этап, и это нормально. Давайте зафиксируем: с какого участка начинаем, кто готовит внутреннее согласование, нужна ли демонстрация со специалистом и когда удобно вернуться с обратной связью. Логичный следующий шаг — демо и коммерческое предложение на пилот.</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Давайте следующим шагом сделаем демонстрацию со специалистом именно на ваших расчётках — а после этого уже КП на пилот. Вам так нормально?</t>
+          <t>Предлагаю следующим шагом провести демонстрацию со специалистом на ваших сценариях по расчётным листкам, а после этого подготовить КП на пилот. Вам такой порядок удобен?</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Давайте на демо разберём кадровые сценарии и параллельно наметим, с какого отдела стартуем. После демо подготовим КП и как будем обучать людей.</t>
+          <t>Предлагаю провести демо на кадровых сценариях и одновременно определить пилотный отдел. После демонстрации подготовим коммерческое предложение и план обучения.</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Давайте технически ещё раз всё покажем — с ответами для ИБ — и потом оценим пилот. Подскажите, какие документы вам от нас нужны, чтобы внутри согласовать?</t>
+          <t>Предлагаю техническую демонстрацию с ответами на вопросы ИБ и затем оценку пилота. Какие документы от нас потребуются для внутреннего согласования?</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>6. СМАРТВЕЙ — тоже коротко, без продажи сходу</t>
+          <t>6. СМАРТВЕЙ — кратко квалифицируем и передаём коллеге</t>
         </is>
       </c>
       <c r="B26" s="4" t="n"/>
@@ -2305,7 +2304,7 @@
       <c r="D26" s="4" t="n"/>
       <c r="E26" s="4" t="n"/>
     </row>
-    <row r="27" ht="90" customHeight="1">
+    <row r="27" ht="95" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
           <t>Вопросы Смартвей</t>
@@ -2313,22 +2312,22 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>А скажите, командировки у вас регулярные — по филиалам, на объекты? Как сейчас организуете: агентство, несколько сервисов, или руками? И кто этим живёт — админы, финансы?</t>
+          <t>Подскажите, командировки в компании регулярны — по филиалам или объектам? Как сейчас организован процесс: агентство, несколько сервисов или вручную? Кто отвечает за это направление — административный блок или финансы?</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>А авансовые как закрываете, когда поездок много? В 1С сами попадают или всё вручную? Это сильно время ест?</t>
+          <t>Как закрываете авансовые отчёты при большом числе поездок? Данные попадают в 1С без ручного ввода, или это отдельная нагрузка на бухгалтерию?</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>А приказы и служебные по командировкам кто оформляет, когда поток большой?</t>
+          <t>Кто оформляет кадровые документы по командировкам при значительном потоке?</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>Скажите, travel с 1С у вас как-то связан, или всё сводите руками? ИБ на такое тоже смотрит?</t>
+          <t>Есть ли сейчас связь travel-сервиса с 1С, или данные сводятся вручную? Потребуется ли согласование службы ИБ?</t>
         </is>
       </c>
     </row>
@@ -2341,26 +2340,26 @@
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>Понял(а) вас. Если командировок много и они регулярные — давайте это отдельно разберём. Есть «Смартвей»: одно окно и нормальная связка с 1С. В крупных компаниях это обычно другой коллега ведёт — я передам контакт и что вы рассказали.</t>
+          <t>Благодарю вас. Если командировки регулярны и их много, этот вопрос лучше разобрать отдельно. Сервис «Смартвей» объединяет организацию поездок и связку с 1С. В корпоративном сегменте его обычно ведёт профильный коллега — я передам контакт и кратко опишу вашу текущую схему.</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>Понял(а). Для бухгалтерии тут как раз про авансовые и меньше ручного ввода в 1С. Точные цифры лучше коллега на отдельном созвоне покажет — я его подключу.</t>
+          <t>Для бухгалтерии ценность в авансовых отчётах и снижении ручного ввода в 1С. Детальный разбор лучше провести с коллегой на отдельной встрече — я его подключу.</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Если поездок много, кадры тоже от документов устают. Могу коллеге передать — пусть покажет, как это с ЗУП стыкуется.</t>
+          <t>При большом потоке командировок растёт и нагрузка на кадровые документы. Могу передать коллеге запрос — он покажет связку с ЗУП.</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>По интеграциям и безопасности коллега схему подготовит. Я ваш контакт передам и список вопросов, которые вы задали.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="60" customHeight="1">
+          <t>По интеграциям и безопасности коллега подготовит схему. Я передам ваш контакт и вопросы, которые вы обозначили.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="55" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Передача коллеге</t>
@@ -2368,22 +2367,22 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Хорошо, спасибо. Этим сервисом занимается другой мой коллега — я передам ваш контакт и коротко расскажу, как у вас сейчас устроено. Он сам напишет и предложит удобное время. Без спама, спокойно.</t>
+          <t>Благодарю вас. Этим сервисом занимается другой коллега — я передам ваш контакт и кратко опишу, как у вас сейчас организован процесс. Он свяжется и предложит удобное время для разговора.</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Хорошо, спасибо. Этим сервисом занимается другой мой коллега — я передам ваш контакт и коротко расскажу, как у вас сейчас устроено. Он сам напишет и предложит удобное время. Без спама, спокойно.</t>
+          <t>Благодарю вас. Этим сервисом занимается другой коллега — я передам ваш контакт и кратко опишу, как у вас сейчас организован процесс. Он свяжется и предложит удобное время для разговора.</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Хорошо, спасибо. Этим сервисом занимается другой мой коллега — я передам ваш контакт и коротко расскажу, как у вас сейчас устроено. Он сам напишет и предложит удобное время. Без спама, спокойно.</t>
+          <t>Благодарю вас. Этим сервисом занимается другой коллега — я передам ваш контакт и кратко опишу, как у вас сейчас организован процесс. Он свяжется и предложит удобное время для разговора.</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Хорошо, спасибо. Этим сервисом занимается другой мой коллега — я передам ваш контакт и коротко расскажу, как у вас сейчас устроено. Он сам напишет и предложит удобное время. Без спама, спокойно.</t>
+          <t>Благодарю вас. Этим сервисом занимается другой коллега — я передам ваш контакт и кратко опишу, как у вас сейчас организован процесс. Он свяжется и предложит удобное время для разговора.</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2397,7 @@
       <c r="D30" s="4" t="n"/>
       <c r="E30" s="4" t="n"/>
     </row>
-    <row r="31" ht="85" customHeight="1">
+    <row r="31" ht="90" customHeight="1">
       <c r="A31" s="9" t="inlineStr">
         <is>
           <t>Финиш звонка</t>
@@ -2406,22 +2405,22 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Спасибо вам большое за время, [ИО]! Давайте сверём: я на почту [e-mail] отправлю материалы, встреча у нас [дата/время], с вашей стороны будут [роли]. Если нужно перенести или кого-то добавить — просто ответьте на письмо. После встречи уже решим по демо и по пилоту. Хорошего дня!</t>
+          <t>Спасибо вам за уделенное время, [ИО]! Давайте сверим договорённости: я направлю материалы на почту [e-mail], встреча — [дата/время], с вашей стороны планируются [роли]. Если потребуется перенести встречу или добавить участника — ответьте, пожалуйста, на письмо. После встречи определим следующий шаг: демонстрацию со специалистом и проработку пилота. Хорошего дня!</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Спасибо вам большое за время, [ИО]! Давайте сверём: я на почту [e-mail] отправлю материалы, встреча у нас [дата/время], с вашей стороны будут [роли]. Если нужно перенести или кого-то добавить — просто ответьте на письмо. После встречи уже решим по демо и по пилоту. Хорошего дня!</t>
+          <t>Спасибо вам за уделенное время, [ИО]! Давайте сверим договорённости: я направлю материалы на почту [e-mail], встреча — [дата/время], с вашей стороны планируются [роли]. Если потребуется перенести встречу или добавить участника — ответьте, пожалуйста, на письмо. После встречи определим следующий шаг: демонстрацию со специалистом и проработку пилота. Хорошего дня!</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>Спасибо вам большое за время, [ИО]! Давайте сверём: я на почту [e-mail] отправлю материалы, встреча у нас [дата/время], с вашей стороны будут [роли]. Если нужно перенести или кого-то добавить — просто ответьте на письмо. После встречи уже решим по демо и по пилоту. Хорошего дня!</t>
+          <t>Спасибо вам за уделенное время, [ИО]! Давайте сверим договорённости: я направлю материалы на почту [e-mail], встреча — [дата/время], с вашей стороны планируются [роли]. Если потребуется перенести встречу или добавить участника — ответьте, пожалуйста, на письмо. После встречи определим следующий шаг: демонстрацию со специалистом и проработку пилота. Хорошего дня!</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>Спасибо вам большое за время, [ИО]! Давайте сверём: я на почту [e-mail] отправлю материалы, встреча у нас [дата/время], с вашей стороны будут [роли]. Если нужно перенести или кого-то добавить — просто ответьте на письмо. После встречи уже решим по демо и по пилоту. Хорошего дня!</t>
+          <t>Спасибо вам за уделенное время, [ИО]! Давайте сверим договорённости: я направлю материалы на почту [e-mail], встреча — [дата/время], с вашей стороны планируются [роли]. Если потребуется перенести встречу или добавить участника — ответьте, пожалуйста, на письмо. После встречи определим следующий шаг: демонстрацию со специалистом и проработку пилота. Хорошего дня!</t>
         </is>
       </c>
     </row>
@@ -2439,7 +2438,7 @@
     <row r="33" ht="48" customHeight="1">
       <c r="A33" s="14" t="inlineStr">
         <is>
-          <t>• На звонке не презентуем. • Письмо на почту — в тот же день. • Встречу и состав согласуем заранее. • Пилот — отдел/филиал/50–100+, не «10 для галочки». • Счёт — после встречи, демо и их согласования. • Цепочка: интерес → встреча → демо → КП → согласование → пилот.</t>
+          <t>• На звонке не проводим презентацию. • Письмо на почту — в тот же день. • Встречу и состав согласуем заранее. • Пилот — отдел, филиал или 50–100+ кабинетов. • Счёт — после встречи, демо и внутреннего согласования. • Цепочка: интерес → встреча → демо → КП → согласование → пилот.</t>
         </is>
       </c>
       <c r="B33" s="14" t="n"/>
@@ -2456,22 +2455,22 @@
       </c>
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>«Пришлите на почту» → «Конечно, так и хотел(а). Смотрите, чтобы письмо было по делу — подтвердите почту и кого ещё в копию поставить. И давайте сразу слот на встречу наметим, пока всё свежее».</t>
+          <t>«Пришлите на почту» — «Конечно, так и планировал(а). Подтвердите, пожалуйста, адрес почты и кого ещё поставить в копию, чтобы письмо сразу ушло нужному составу. И давайте сразу согласуем время встречи, пока материалы актуальны».</t>
         </is>
       </c>
       <c r="C34" s="25" t="inlineStr">
         <is>
-          <t>«Мне нужно согласовать» → «Да, это нормально, у вас же большая компания. Давайте я короткие материалы подготовлю и помогу собрать на встречу тех, без кого обычно дальше не двигается».</t>
+          <t>«Мне нужно согласовать» — «Да, в корпоративном формате это обычный порядок. Я подготовлю краткие материалы и помогу собрать на встречу тех, без кого решение, как правило, не принимается».</t>
         </is>
       </c>
       <c r="D34" s="25" t="inlineStr">
         <is>
-          <t>«Сейчас не до проектов» → «Понимаю вас. Поэтому я как раз не про «давайте всю компанию». Давайте короткую встречу — а дальше, если зайдёт, пилот на один участок, без большой нагрузки на людей».</t>
+          <t>«Сейчас не до проектов» — «Понимаю. Поэтому и не предлагаю перевод всей компании. Давайте проведём короткую встречу, а при интересе рассмотрим пилот на одном участке — без существенной нагрузки на команду».</t>
         </is>
       </c>
       <c r="E34" s="25" t="inlineStr">
         <is>
-          <t>«Нужно через ИБ / закупки» → «Хорошо, давайте сразу это учтём. Скажите, какие документы им нужны — подготовим к встрече или сразу после неё».</t>
+          <t>«Нужно через ИБ / закупки» — «Хорошо, учтём это сразу. Подскажите, какие документы потребуются — подготовим их к встрече или сразу после неё».</t>
         </is>
       </c>
     </row>

--- a/скрипт КабС, ДОКИ, Смартвей.xlsx
+++ b/скрипт КабС, ДОКИ, Смартвей.xlsx
@@ -2405,22 +2405,22 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Спасибо вам за уделенное время, [ИО]! Давайте сверим договорённости: я направлю материалы на почту [e-mail], встреча — [дата/время], с вашей стороны планируются [роли]. Если потребуется перенести встречу или добавить участника — ответьте, пожалуйста, на письмо. После встречи определим следующий шаг: демонстрацию со специалистом и проработку пилота. Хорошего дня!</t>
+          <t>Спасибо вам за уделённое время, [ИО]! Давайте сверим договорённости: я направлю материалы на почту [e-mail], встреча — [дата/время], с вашей стороны планируются [роли]. Если потребуется перенести встречу или добавить участника — ответьте, пожалуйста, на письмо. После встречи определим следующий шаг: демонстрацию со специалистом и проработку пилота. Хорошего дня!</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Спасибо вам за уделенное время, [ИО]! Давайте сверим договорённости: я направлю материалы на почту [e-mail], встреча — [дата/время], с вашей стороны планируются [роли]. Если потребуется перенести встречу или добавить участника — ответьте, пожалуйста, на письмо. После встречи определим следующий шаг: демонстрацию со специалистом и проработку пилота. Хорошего дня!</t>
+          <t>Спасибо вам за уделённое время, [ИО]! Давайте сверим договорённости: я направлю материалы на почту [e-mail], встреча — [дата/время], с вашей стороны планируются [роли]. Если потребуется перенести встречу или добавить участника — ответьте, пожалуйста, на письмо. После встречи определим следующий шаг: демонстрацию со специалистом и проработку пилота. Хорошего дня!</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>Спасибо вам за уделенное время, [ИО]! Давайте сверим договорённости: я направлю материалы на почту [e-mail], встреча — [дата/время], с вашей стороны планируются [роли]. Если потребуется перенести встречу или добавить участника — ответьте, пожалуйста, на письмо. После встречи определим следующий шаг: демонстрацию со специалистом и проработку пилота. Хорошего дня!</t>
+          <t>Спасибо вам за уделённое время, [ИО]! Давайте сверим договорённости: я направлю материалы на почту [e-mail], встреча — [дата/время], с вашей стороны планируются [роли]. Если потребуется перенести встречу или добавить участника — ответьте, пожалуйста, на письмо. После встречи определим следующий шаг: демонстрацию со специалистом и проработку пилота. Хорошего дня!</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>Спасибо вам за уделенное время, [ИО]! Давайте сверим договорённости: я направлю материалы на почту [e-mail], встреча — [дата/время], с вашей стороны планируются [роли]. Если потребуется перенести встречу или добавить участника — ответьте, пожалуйста, на письмо. После встречи определим следующий шаг: демонстрацию со специалистом и проработку пилота. Хорошего дня!</t>
+          <t>Спасибо вам за уделённое время, [ИО]! Давайте сверим договорённости: я направлю материалы на почту [e-mail], встреча — [дата/время], с вашей стороны планируются [роли]. Если потребуется перенести встречу или добавить участника — ответьте, пожалуйста, на письмо. После встречи определим следующий шаг: демонстрацию со специалистом и проработку пилота. Хорошего дня!</t>
         </is>
       </c>
     </row>
